--- a/tests/eindhoven-500/reference/resultaten/werk/alle groepen/herkomsten/restdag/Pot_totaal_Auto_OV_Fiets.xlsx
+++ b/tests/eindhoven-500/reference/resultaten/werk/alle groepen/herkomsten/restdag/Pot_totaal_Auto_OV_Fiets.xlsx
@@ -391,10 +391,10 @@
         <v>26215</v>
       </c>
       <c r="D2">
-        <v>45658</v>
+        <v>45685</v>
       </c>
       <c r="E2">
-        <v>66064</v>
+        <v>66236</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -405,13 +405,13 @@
         <v>17857</v>
       </c>
       <c r="C3">
-        <v>26898</v>
+        <v>26901</v>
       </c>
       <c r="D3">
-        <v>47245</v>
+        <v>47275</v>
       </c>
       <c r="E3">
-        <v>68736</v>
+        <v>68932</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -422,13 +422,13 @@
         <v>14363</v>
       </c>
       <c r="C4">
-        <v>22438</v>
+        <v>22439</v>
       </c>
       <c r="D4">
-        <v>42227</v>
+        <v>42250</v>
       </c>
       <c r="E4">
-        <v>63132</v>
+        <v>63272</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -439,13 +439,13 @@
         <v>14363</v>
       </c>
       <c r="C5">
-        <v>22438</v>
+        <v>22439</v>
       </c>
       <c r="D5">
-        <v>42227</v>
+        <v>42250</v>
       </c>
       <c r="E5">
-        <v>63132</v>
+        <v>63272</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -456,13 +456,13 @@
         <v>14363</v>
       </c>
       <c r="C6">
-        <v>22438</v>
+        <v>22439</v>
       </c>
       <c r="D6">
-        <v>42227</v>
+        <v>42250</v>
       </c>
       <c r="E6">
-        <v>63132</v>
+        <v>63272</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -473,13 +473,13 @@
         <v>17532</v>
       </c>
       <c r="C7">
-        <v>26201</v>
+        <v>26205</v>
       </c>
       <c r="D7">
-        <v>46011</v>
+        <v>46045</v>
       </c>
       <c r="E7">
-        <v>67004</v>
+        <v>67209</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -490,13 +490,13 @@
         <v>17532</v>
       </c>
       <c r="C8">
-        <v>26201</v>
+        <v>26205</v>
       </c>
       <c r="D8">
-        <v>46011</v>
+        <v>46045</v>
       </c>
       <c r="E8">
-        <v>67004</v>
+        <v>67209</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -507,13 +507,13 @@
         <v>17214</v>
       </c>
       <c r="C9">
-        <v>25526</v>
+        <v>25531</v>
       </c>
       <c r="D9">
-        <v>44793</v>
+        <v>44830</v>
       </c>
       <c r="E9">
-        <v>65258</v>
+        <v>65471</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -524,13 +524,13 @@
         <v>17532</v>
       </c>
       <c r="C10">
-        <v>26201</v>
+        <v>26205</v>
       </c>
       <c r="D10">
-        <v>46011</v>
+        <v>46045</v>
       </c>
       <c r="E10">
-        <v>67004</v>
+        <v>67209</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -541,13 +541,13 @@
         <v>17532</v>
       </c>
       <c r="C11">
-        <v>26201</v>
+        <v>26205</v>
       </c>
       <c r="D11">
-        <v>46011</v>
+        <v>46045</v>
       </c>
       <c r="E11">
-        <v>67004</v>
+        <v>67209</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -558,13 +558,13 @@
         <v>14363</v>
       </c>
       <c r="C12">
-        <v>22438</v>
+        <v>22439</v>
       </c>
       <c r="D12">
-        <v>42227</v>
+        <v>42250</v>
       </c>
       <c r="E12">
-        <v>63132</v>
+        <v>63272</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -575,13 +575,13 @@
         <v>17857</v>
       </c>
       <c r="C13">
-        <v>26898</v>
+        <v>26901</v>
       </c>
       <c r="D13">
-        <v>47245</v>
+        <v>47275</v>
       </c>
       <c r="E13">
-        <v>68736</v>
+        <v>68932</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -592,13 +592,13 @@
         <v>14363</v>
       </c>
       <c r="C14">
-        <v>22438</v>
+        <v>22439</v>
       </c>
       <c r="D14">
-        <v>42227</v>
+        <v>42250</v>
       </c>
       <c r="E14">
-        <v>63132</v>
+        <v>63272</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -609,13 +609,13 @@
         <v>17532</v>
       </c>
       <c r="C15">
-        <v>26201</v>
+        <v>26205</v>
       </c>
       <c r="D15">
-        <v>46011</v>
+        <v>46045</v>
       </c>
       <c r="E15">
-        <v>67004</v>
+        <v>67209</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -629,10 +629,10 @@
         <v>25506</v>
       </c>
       <c r="D16">
-        <v>44407</v>
+        <v>44436</v>
       </c>
       <c r="E16">
-        <v>64290</v>
+        <v>64468</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -643,13 +643,13 @@
         <v>14363</v>
       </c>
       <c r="C17">
-        <v>22438</v>
+        <v>22439</v>
       </c>
       <c r="D17">
-        <v>42227</v>
+        <v>42250</v>
       </c>
       <c r="E17">
-        <v>63132</v>
+        <v>63272</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -660,13 +660,13 @@
         <v>17857</v>
       </c>
       <c r="C18">
-        <v>26898</v>
+        <v>26901</v>
       </c>
       <c r="D18">
-        <v>47245</v>
+        <v>47275</v>
       </c>
       <c r="E18">
-        <v>68736</v>
+        <v>68932</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -680,10 +680,10 @@
         <v>25506</v>
       </c>
       <c r="D19">
-        <v>44407</v>
+        <v>44436</v>
       </c>
       <c r="E19">
-        <v>64290</v>
+        <v>64468</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -697,10 +697,10 @@
         <v>25506</v>
       </c>
       <c r="D20">
-        <v>44407</v>
+        <v>44436</v>
       </c>
       <c r="E20">
-        <v>64290</v>
+        <v>64468</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -714,10 +714,10 @@
         <v>25506</v>
       </c>
       <c r="D21">
-        <v>44407</v>
+        <v>44436</v>
       </c>
       <c r="E21">
-        <v>64290</v>
+        <v>64468</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -728,13 +728,13 @@
         <v>20999</v>
       </c>
       <c r="C22">
-        <v>31394</v>
+        <v>31476</v>
       </c>
       <c r="D22">
-        <v>53110</v>
+        <v>53355</v>
       </c>
       <c r="E22">
-        <v>75155</v>
+        <v>75623</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -748,10 +748,10 @@
         <v>26215</v>
       </c>
       <c r="D23">
-        <v>45658</v>
+        <v>45685</v>
       </c>
       <c r="E23">
-        <v>66064</v>
+        <v>66236</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -762,13 +762,13 @@
         <v>10353</v>
       </c>
       <c r="C24">
-        <v>16735</v>
+        <v>16736</v>
       </c>
       <c r="D24">
-        <v>34920</v>
+        <v>34946</v>
       </c>
       <c r="E24">
-        <v>53316</v>
+        <v>53390</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -779,13 +779,13 @@
         <v>10353</v>
       </c>
       <c r="C25">
-        <v>16735</v>
+        <v>16736</v>
       </c>
       <c r="D25">
-        <v>34920</v>
+        <v>34946</v>
       </c>
       <c r="E25">
-        <v>53316</v>
+        <v>53390</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -796,13 +796,13 @@
         <v>10353</v>
       </c>
       <c r="C26">
-        <v>16735</v>
+        <v>16736</v>
       </c>
       <c r="D26">
-        <v>34920</v>
+        <v>34946</v>
       </c>
       <c r="E26">
-        <v>53316</v>
+        <v>53390</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -816,10 +816,10 @@
         <v>24709</v>
       </c>
       <c r="D27">
-        <v>43594</v>
+        <v>43670</v>
       </c>
       <c r="E27">
-        <v>64298</v>
+        <v>64477</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -833,10 +833,10 @@
         <v>24709</v>
       </c>
       <c r="D28">
-        <v>43594</v>
+        <v>43670</v>
       </c>
       <c r="E28">
-        <v>64298</v>
+        <v>64477</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -850,10 +850,10 @@
         <v>24709</v>
       </c>
       <c r="D29">
-        <v>43594</v>
+        <v>43670</v>
       </c>
       <c r="E29">
-        <v>64298</v>
+        <v>64477</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -864,13 +864,13 @@
         <v>28821</v>
       </c>
       <c r="C30">
-        <v>36863</v>
+        <v>36944</v>
       </c>
       <c r="D30">
-        <v>56526</v>
+        <v>56856</v>
       </c>
       <c r="E30">
-        <v>78595</v>
+        <v>78962</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -881,13 +881,13 @@
         <v>28821</v>
       </c>
       <c r="C31">
-        <v>36863</v>
+        <v>36944</v>
       </c>
       <c r="D31">
-        <v>56526</v>
+        <v>56856</v>
       </c>
       <c r="E31">
-        <v>78595</v>
+        <v>78962</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -898,13 +898,13 @@
         <v>29232</v>
       </c>
       <c r="C32">
-        <v>37670</v>
+        <v>37751</v>
       </c>
       <c r="D32">
-        <v>57731</v>
+        <v>58048</v>
       </c>
       <c r="E32">
-        <v>79959</v>
+        <v>80311</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -915,13 +915,13 @@
         <v>28821</v>
       </c>
       <c r="C33">
-        <v>36863</v>
+        <v>36944</v>
       </c>
       <c r="D33">
-        <v>56526</v>
+        <v>56856</v>
       </c>
       <c r="E33">
-        <v>78595</v>
+        <v>78962</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -929,16 +929,16 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>33975</v>
+        <v>33990</v>
       </c>
       <c r="C34">
-        <v>42165</v>
+        <v>42313</v>
       </c>
       <c r="D34">
-        <v>61919</v>
+        <v>62256</v>
       </c>
       <c r="E34">
-        <v>83942</v>
+        <v>84202</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -949,13 +949,13 @@
         <v>35252</v>
       </c>
       <c r="C35">
-        <v>43575</v>
+        <v>43644</v>
       </c>
       <c r="D35">
-        <v>63263</v>
+        <v>63630</v>
       </c>
       <c r="E35">
-        <v>85018</v>
+        <v>85276</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -966,13 +966,13 @@
         <v>25066</v>
       </c>
       <c r="C36">
-        <v>33053</v>
+        <v>33094</v>
       </c>
       <c r="D36">
-        <v>53520</v>
+        <v>53695</v>
       </c>
       <c r="E36">
-        <v>76444</v>
+        <v>76696</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -983,13 +983,13 @@
         <v>29538</v>
       </c>
       <c r="C37">
-        <v>37610</v>
+        <v>37682</v>
       </c>
       <c r="D37">
-        <v>56962</v>
+        <v>57375</v>
       </c>
       <c r="E37">
-        <v>78847</v>
+        <v>79230</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1000,13 +1000,13 @@
         <v>29538</v>
       </c>
       <c r="C38">
-        <v>37610</v>
+        <v>37682</v>
       </c>
       <c r="D38">
-        <v>56962</v>
+        <v>57375</v>
       </c>
       <c r="E38">
-        <v>78847</v>
+        <v>79230</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1014,16 +1014,16 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>33549</v>
+        <v>33564</v>
       </c>
       <c r="C39">
-        <v>41389</v>
+        <v>41537</v>
       </c>
       <c r="D39">
-        <v>60752</v>
+        <v>61108</v>
       </c>
       <c r="E39">
-        <v>82686</v>
+        <v>82969</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1034,13 +1034,13 @@
         <v>35252</v>
       </c>
       <c r="C40">
-        <v>43575</v>
+        <v>43644</v>
       </c>
       <c r="D40">
-        <v>63263</v>
+        <v>63630</v>
       </c>
       <c r="E40">
-        <v>85018</v>
+        <v>85276</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1051,13 +1051,13 @@
         <v>35252</v>
       </c>
       <c r="C41">
-        <v>43575</v>
+        <v>43644</v>
       </c>
       <c r="D41">
-        <v>63263</v>
+        <v>63630</v>
       </c>
       <c r="E41">
-        <v>85018</v>
+        <v>85276</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -1068,13 +1068,13 @@
         <v>26633</v>
       </c>
       <c r="C42">
-        <v>34921</v>
+        <v>34971</v>
       </c>
       <c r="D42">
-        <v>55187</v>
+        <v>55594</v>
       </c>
       <c r="E42">
-        <v>77858</v>
+        <v>78285</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1085,13 +1085,13 @@
         <v>27068</v>
       </c>
       <c r="C43">
-        <v>35747</v>
+        <v>35796</v>
       </c>
       <c r="D43">
-        <v>56424</v>
+        <v>56814</v>
       </c>
       <c r="E43">
-        <v>79254</v>
+        <v>79654</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1102,13 +1102,13 @@
         <v>25135</v>
       </c>
       <c r="C44">
-        <v>34178</v>
+        <v>34286</v>
       </c>
       <c r="D44">
-        <v>55572</v>
+        <v>56022</v>
       </c>
       <c r="E44">
-        <v>78706</v>
+        <v>79201</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1119,13 +1119,13 @@
         <v>24242</v>
       </c>
       <c r="C45">
-        <v>32244</v>
+        <v>32257</v>
       </c>
       <c r="D45">
-        <v>52623</v>
+        <v>52859</v>
       </c>
       <c r="E45">
-        <v>75301</v>
+        <v>75594</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1136,13 +1136,13 @@
         <v>29978</v>
       </c>
       <c r="C46">
-        <v>38425</v>
+        <v>38496</v>
       </c>
       <c r="D46">
-        <v>58156</v>
+        <v>58555</v>
       </c>
       <c r="E46">
-        <v>80205</v>
+        <v>80565</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1153,13 +1153,13 @@
         <v>25420</v>
       </c>
       <c r="C47">
-        <v>33806</v>
+        <v>33847</v>
       </c>
       <c r="D47">
-        <v>54725</v>
+        <v>54894</v>
       </c>
       <c r="E47">
-        <v>77850</v>
+        <v>78091</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1170,13 +1170,13 @@
         <v>24634</v>
       </c>
       <c r="C48">
-        <v>33036</v>
+        <v>33049</v>
       </c>
       <c r="D48">
-        <v>53852</v>
+        <v>54080</v>
       </c>
       <c r="E48">
-        <v>76740</v>
+        <v>77017</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -1187,13 +1187,13 @@
         <v>19561</v>
       </c>
       <c r="C49">
-        <v>27234</v>
+        <v>27254</v>
       </c>
       <c r="D49">
-        <v>41910</v>
+        <v>41980</v>
       </c>
       <c r="E49">
-        <v>56940</v>
+        <v>56977</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -1207,10 +1207,10 @@
         <v>27949</v>
       </c>
       <c r="D50">
-        <v>43063</v>
+        <v>43070</v>
       </c>
       <c r="E50">
-        <v>58846</v>
+        <v>58856</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -1221,13 +1221,13 @@
         <v>14627</v>
       </c>
       <c r="C51">
-        <v>21771</v>
+        <v>21785</v>
       </c>
       <c r="D51">
-        <v>36997</v>
+        <v>37082</v>
       </c>
       <c r="E51">
-        <v>51584</v>
+        <v>51651</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -1238,13 +1238,13 @@
         <v>15607</v>
       </c>
       <c r="C52">
-        <v>23289</v>
+        <v>23351</v>
       </c>
       <c r="D52">
-        <v>38985</v>
+        <v>39093</v>
       </c>
       <c r="E52">
-        <v>54489</v>
+        <v>54592</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -1255,13 +1255,13 @@
         <v>15438</v>
       </c>
       <c r="C53">
-        <v>22476</v>
+        <v>22482</v>
       </c>
       <c r="D53">
-        <v>37523</v>
+        <v>37595</v>
       </c>
       <c r="E53">
-        <v>52244</v>
+        <v>52283</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1272,13 +1272,13 @@
         <v>14336</v>
       </c>
       <c r="C54">
-        <v>21183</v>
+        <v>21196</v>
       </c>
       <c r="D54">
-        <v>35989</v>
+        <v>36081</v>
       </c>
       <c r="E54">
-        <v>50028</v>
+        <v>50099</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -1292,10 +1292,10 @@
         <v>27949</v>
       </c>
       <c r="D55">
-        <v>43063</v>
+        <v>43070</v>
       </c>
       <c r="E55">
-        <v>58846</v>
+        <v>58856</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -1306,13 +1306,13 @@
         <v>21155</v>
       </c>
       <c r="C56">
-        <v>29198</v>
+        <v>29251</v>
       </c>
       <c r="D56">
-        <v>44957</v>
+        <v>45047</v>
       </c>
       <c r="E56">
-        <v>61732</v>
+        <v>61870</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -1323,13 +1323,13 @@
         <v>14234</v>
       </c>
       <c r="C57">
-        <v>21505</v>
+        <v>21515</v>
       </c>
       <c r="D57">
-        <v>37873</v>
+        <v>37950</v>
       </c>
       <c r="E57">
-        <v>54320</v>
+        <v>54380</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -1343,10 +1343,10 @@
         <v>26578</v>
       </c>
       <c r="D58">
-        <v>43055</v>
+        <v>43078</v>
       </c>
       <c r="E58">
-        <v>61752</v>
+        <v>61865</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -1360,10 +1360,10 @@
         <v>26578</v>
       </c>
       <c r="D59">
-        <v>43055</v>
+        <v>43078</v>
       </c>
       <c r="E59">
-        <v>61752</v>
+        <v>61865</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -1377,10 +1377,10 @@
         <v>17424</v>
       </c>
       <c r="D60">
-        <v>33952</v>
+        <v>33976</v>
       </c>
       <c r="E60">
-        <v>51002</v>
+        <v>51043</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -1394,10 +1394,10 @@
         <v>17424</v>
       </c>
       <c r="D61">
-        <v>33952</v>
+        <v>33976</v>
       </c>
       <c r="E61">
-        <v>51002</v>
+        <v>51043</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -1408,13 +1408,13 @@
         <v>5771</v>
       </c>
       <c r="C62">
-        <v>10768</v>
+        <v>10769</v>
       </c>
       <c r="D62">
-        <v>28663</v>
+        <v>28676</v>
       </c>
       <c r="E62">
-        <v>47077</v>
+        <v>47114</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -1425,13 +1425,13 @@
         <v>5771</v>
       </c>
       <c r="C63">
-        <v>10768</v>
+        <v>10769</v>
       </c>
       <c r="D63">
-        <v>28663</v>
+        <v>28676</v>
       </c>
       <c r="E63">
-        <v>47077</v>
+        <v>47114</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -1442,13 +1442,13 @@
         <v>4170</v>
       </c>
       <c r="C64">
-        <v>8933</v>
+        <v>8936</v>
       </c>
       <c r="D64">
-        <v>26379</v>
+        <v>26390</v>
       </c>
       <c r="E64">
-        <v>44046</v>
+        <v>44075</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -1459,13 +1459,13 @@
         <v>4170</v>
       </c>
       <c r="C65">
-        <v>8933</v>
+        <v>8936</v>
       </c>
       <c r="D65">
-        <v>26379</v>
+        <v>26390</v>
       </c>
       <c r="E65">
-        <v>44046</v>
+        <v>44075</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -1476,13 +1476,13 @@
         <v>19365</v>
       </c>
       <c r="C66">
-        <v>27799</v>
+        <v>27813</v>
       </c>
       <c r="D66">
-        <v>49559</v>
+        <v>49651</v>
       </c>
       <c r="E66">
-        <v>73297</v>
+        <v>73549</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -1493,13 +1493,13 @@
         <v>19716</v>
       </c>
       <c r="C67">
-        <v>28551</v>
+        <v>28564</v>
       </c>
       <c r="D67">
-        <v>50817</v>
+        <v>50904</v>
       </c>
       <c r="E67">
-        <v>74831</v>
+        <v>75074</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -1510,13 +1510,13 @@
         <v>19365</v>
       </c>
       <c r="C68">
-        <v>27799</v>
+        <v>27813</v>
       </c>
       <c r="D68">
-        <v>49559</v>
+        <v>49651</v>
       </c>
       <c r="E68">
-        <v>73297</v>
+        <v>73549</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -1527,13 +1527,13 @@
         <v>19716</v>
       </c>
       <c r="C69">
-        <v>28551</v>
+        <v>28564</v>
       </c>
       <c r="D69">
-        <v>50817</v>
+        <v>50904</v>
       </c>
       <c r="E69">
-        <v>74831</v>
+        <v>75074</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -1544,13 +1544,13 @@
         <v>19716</v>
       </c>
       <c r="C70">
-        <v>28551</v>
+        <v>28564</v>
       </c>
       <c r="D70">
-        <v>50817</v>
+        <v>50904</v>
       </c>
       <c r="E70">
-        <v>74831</v>
+        <v>75074</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -1561,13 +1561,13 @@
         <v>21627</v>
       </c>
       <c r="C71">
-        <v>31164</v>
+        <v>31176</v>
       </c>
       <c r="D71">
-        <v>54091</v>
+        <v>54191</v>
       </c>
       <c r="E71">
-        <v>78104</v>
+        <v>78348</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -1578,13 +1578,13 @@
         <v>19716</v>
       </c>
       <c r="C72">
-        <v>28551</v>
+        <v>28564</v>
       </c>
       <c r="D72">
-        <v>50817</v>
+        <v>50904</v>
       </c>
       <c r="E72">
-        <v>74831</v>
+        <v>75074</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -1595,13 +1595,13 @@
         <v>19716</v>
       </c>
       <c r="C73">
-        <v>28551</v>
+        <v>28564</v>
       </c>
       <c r="D73">
-        <v>50817</v>
+        <v>50904</v>
       </c>
       <c r="E73">
-        <v>74831</v>
+        <v>75074</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -1612,13 +1612,13 @@
         <v>19716</v>
       </c>
       <c r="C74">
-        <v>28551</v>
+        <v>28564</v>
       </c>
       <c r="D74">
-        <v>50817</v>
+        <v>50904</v>
       </c>
       <c r="E74">
-        <v>74831</v>
+        <v>75074</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -1629,13 +1629,13 @@
         <v>13711</v>
       </c>
       <c r="C75">
-        <v>20566</v>
+        <v>20567</v>
       </c>
       <c r="D75">
-        <v>40884</v>
+        <v>40920</v>
       </c>
       <c r="E75">
-        <v>64125</v>
+        <v>64333</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -1646,13 +1646,13 @@
         <v>19716</v>
       </c>
       <c r="C76">
-        <v>28551</v>
+        <v>28564</v>
       </c>
       <c r="D76">
-        <v>50817</v>
+        <v>50904</v>
       </c>
       <c r="E76">
-        <v>74831</v>
+        <v>75074</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -1663,13 +1663,13 @@
         <v>18690</v>
       </c>
       <c r="C77">
-        <v>27300</v>
+        <v>27302</v>
       </c>
       <c r="D77">
-        <v>49800</v>
+        <v>49873</v>
       </c>
       <c r="E77">
-        <v>74148</v>
+        <v>74374</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -1680,13 +1680,13 @@
         <v>18690</v>
       </c>
       <c r="C78">
-        <v>27300</v>
+        <v>27302</v>
       </c>
       <c r="D78">
-        <v>49800</v>
+        <v>49873</v>
       </c>
       <c r="E78">
-        <v>74148</v>
+        <v>74374</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -1697,13 +1697,13 @@
         <v>18690</v>
       </c>
       <c r="C79">
-        <v>27300</v>
+        <v>27302</v>
       </c>
       <c r="D79">
-        <v>49800</v>
+        <v>49873</v>
       </c>
       <c r="E79">
-        <v>74148</v>
+        <v>74374</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -1714,13 +1714,13 @@
         <v>18690</v>
       </c>
       <c r="C80">
-        <v>27300</v>
+        <v>27302</v>
       </c>
       <c r="D80">
-        <v>49800</v>
+        <v>49873</v>
       </c>
       <c r="E80">
-        <v>74148</v>
+        <v>74374</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -1731,13 +1731,13 @@
         <v>28041</v>
       </c>
       <c r="C81">
-        <v>36818</v>
+        <v>36825</v>
       </c>
       <c r="D81">
-        <v>57067</v>
+        <v>57176</v>
       </c>
       <c r="E81">
-        <v>78965</v>
+        <v>79142</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -1748,13 +1748,13 @@
         <v>28041</v>
       </c>
       <c r="C82">
-        <v>36818</v>
+        <v>36825</v>
       </c>
       <c r="D82">
-        <v>57067</v>
+        <v>57176</v>
       </c>
       <c r="E82">
-        <v>78965</v>
+        <v>79142</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -1768,10 +1768,10 @@
         <v>24161</v>
       </c>
       <c r="D83">
-        <v>44154</v>
+        <v>44261</v>
       </c>
       <c r="E83">
-        <v>66455</v>
+        <v>66745</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -1785,10 +1785,10 @@
         <v>24161</v>
       </c>
       <c r="D84">
-        <v>44154</v>
+        <v>44261</v>
       </c>
       <c r="E84">
-        <v>66455</v>
+        <v>66745</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -1799,13 +1799,13 @@
         <v>26942</v>
       </c>
       <c r="C85">
-        <v>35571</v>
+        <v>35577</v>
       </c>
       <c r="D85">
-        <v>55574</v>
+        <v>56068</v>
       </c>
       <c r="E85">
-        <v>77408</v>
+        <v>77910</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -1816,13 +1816,13 @@
         <v>26942</v>
       </c>
       <c r="C86">
-        <v>35571</v>
+        <v>35577</v>
       </c>
       <c r="D86">
-        <v>55574</v>
+        <v>56068</v>
       </c>
       <c r="E86">
-        <v>77408</v>
+        <v>77910</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -1833,13 +1833,13 @@
         <v>25806</v>
       </c>
       <c r="C87">
-        <v>34976</v>
+        <v>35065</v>
       </c>
       <c r="D87">
-        <v>56265</v>
+        <v>56857</v>
       </c>
       <c r="E87">
-        <v>78639</v>
+        <v>79189</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -1850,13 +1850,13 @@
         <v>25806</v>
       </c>
       <c r="C88">
-        <v>34976</v>
+        <v>35065</v>
       </c>
       <c r="D88">
-        <v>56265</v>
+        <v>56857</v>
       </c>
       <c r="E88">
-        <v>78639</v>
+        <v>79189</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -1867,13 +1867,13 @@
         <v>25806</v>
       </c>
       <c r="C89">
-        <v>34976</v>
+        <v>35065</v>
       </c>
       <c r="D89">
-        <v>56265</v>
+        <v>56857</v>
       </c>
       <c r="E89">
-        <v>78639</v>
+        <v>79189</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -1881,16 +1881,16 @@
         <v>89</v>
       </c>
       <c r="B90">
-        <v>55671</v>
+        <v>55672</v>
       </c>
       <c r="C90">
-        <v>63808</v>
+        <v>63821</v>
       </c>
       <c r="D90">
-        <v>78543</v>
+        <v>78594</v>
       </c>
       <c r="E90">
-        <v>94766</v>
+        <v>94809</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -1898,16 +1898,16 @@
         <v>90</v>
       </c>
       <c r="B91">
-        <v>55671</v>
+        <v>55672</v>
       </c>
       <c r="C91">
-        <v>63808</v>
+        <v>63821</v>
       </c>
       <c r="D91">
-        <v>78543</v>
+        <v>78594</v>
       </c>
       <c r="E91">
-        <v>94766</v>
+        <v>94809</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -1915,16 +1915,16 @@
         <v>91</v>
       </c>
       <c r="B92">
-        <v>55671</v>
+        <v>55672</v>
       </c>
       <c r="C92">
-        <v>63808</v>
+        <v>63821</v>
       </c>
       <c r="D92">
-        <v>78543</v>
+        <v>78594</v>
       </c>
       <c r="E92">
-        <v>94766</v>
+        <v>94809</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -1932,16 +1932,16 @@
         <v>92</v>
       </c>
       <c r="B93">
-        <v>55671</v>
+        <v>55672</v>
       </c>
       <c r="C93">
-        <v>63808</v>
+        <v>63821</v>
       </c>
       <c r="D93">
-        <v>78543</v>
+        <v>78594</v>
       </c>
       <c r="E93">
-        <v>94766</v>
+        <v>94809</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -1952,13 +1952,13 @@
         <v>56619</v>
       </c>
       <c r="C94">
-        <v>65287</v>
+        <v>65302</v>
       </c>
       <c r="D94">
-        <v>79707</v>
+        <v>79761</v>
       </c>
       <c r="E94">
-        <v>95411</v>
+        <v>95456</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -1966,16 +1966,16 @@
         <v>94</v>
       </c>
       <c r="B95">
-        <v>55671</v>
+        <v>55672</v>
       </c>
       <c r="C95">
-        <v>63808</v>
+        <v>63821</v>
       </c>
       <c r="D95">
-        <v>78543</v>
+        <v>78594</v>
       </c>
       <c r="E95">
-        <v>94766</v>
+        <v>94809</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -1983,16 +1983,16 @@
         <v>95</v>
       </c>
       <c r="B96">
-        <v>55671</v>
+        <v>55672</v>
       </c>
       <c r="C96">
-        <v>63808</v>
+        <v>63821</v>
       </c>
       <c r="D96">
-        <v>78543</v>
+        <v>78594</v>
       </c>
       <c r="E96">
-        <v>94766</v>
+        <v>94809</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -2000,16 +2000,16 @@
         <v>96</v>
       </c>
       <c r="B97">
-        <v>55671</v>
+        <v>55672</v>
       </c>
       <c r="C97">
-        <v>63808</v>
+        <v>63821</v>
       </c>
       <c r="D97">
-        <v>78543</v>
+        <v>78594</v>
       </c>
       <c r="E97">
-        <v>94766</v>
+        <v>94809</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -2020,13 +2020,13 @@
         <v>53353</v>
       </c>
       <c r="C98">
-        <v>62368</v>
+        <v>62389</v>
       </c>
       <c r="D98">
-        <v>78640</v>
+        <v>78742</v>
       </c>
       <c r="E98">
-        <v>95093</v>
+        <v>95169</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -2037,13 +2037,13 @@
         <v>53353</v>
       </c>
       <c r="C99">
-        <v>62368</v>
+        <v>62389</v>
       </c>
       <c r="D99">
-        <v>78640</v>
+        <v>78742</v>
       </c>
       <c r="E99">
-        <v>95093</v>
+        <v>95169</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -2054,13 +2054,13 @@
         <v>53168</v>
       </c>
       <c r="C100">
-        <v>61438</v>
+        <v>61453</v>
       </c>
       <c r="D100">
-        <v>77377</v>
+        <v>77464</v>
       </c>
       <c r="E100">
-        <v>94188</v>
+        <v>94256</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -2071,13 +2071,13 @@
         <v>53168</v>
       </c>
       <c r="C101">
-        <v>61438</v>
+        <v>61453</v>
       </c>
       <c r="D101">
-        <v>77377</v>
+        <v>77464</v>
       </c>
       <c r="E101">
-        <v>94188</v>
+        <v>94256</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -2088,13 +2088,13 @@
         <v>53168</v>
       </c>
       <c r="C102">
-        <v>61438</v>
+        <v>61453</v>
       </c>
       <c r="D102">
-        <v>77377</v>
+        <v>77464</v>
       </c>
       <c r="E102">
-        <v>94188</v>
+        <v>94256</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -2105,13 +2105,13 @@
         <v>50510</v>
       </c>
       <c r="C103">
-        <v>59920</v>
+        <v>59980</v>
       </c>
       <c r="D103">
-        <v>77169</v>
+        <v>77341</v>
       </c>
       <c r="E103">
-        <v>94109</v>
+        <v>94210</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -2122,13 +2122,13 @@
         <v>50510</v>
       </c>
       <c r="C104">
-        <v>59920</v>
+        <v>59980</v>
       </c>
       <c r="D104">
-        <v>77169</v>
+        <v>77341</v>
       </c>
       <c r="E104">
-        <v>94109</v>
+        <v>94210</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -2139,13 +2139,13 @@
         <v>50834</v>
       </c>
       <c r="C105">
-        <v>59906</v>
+        <v>59907</v>
       </c>
       <c r="D105">
-        <v>77253</v>
+        <v>77329</v>
       </c>
       <c r="E105">
-        <v>94430</v>
+        <v>94507</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -2156,13 +2156,13 @@
         <v>51673</v>
       </c>
       <c r="C106">
-        <v>61996</v>
+        <v>62054</v>
       </c>
       <c r="D106">
-        <v>79515</v>
+        <v>79671</v>
       </c>
       <c r="E106">
-        <v>95958</v>
+        <v>96042</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -2173,13 +2173,13 @@
         <v>51673</v>
       </c>
       <c r="C107">
-        <v>61996</v>
+        <v>62054</v>
       </c>
       <c r="D107">
-        <v>79515</v>
+        <v>79671</v>
       </c>
       <c r="E107">
-        <v>95958</v>
+        <v>96042</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -2190,13 +2190,13 @@
         <v>51944</v>
       </c>
       <c r="C108">
-        <v>61936</v>
+        <v>61937</v>
       </c>
       <c r="D108">
-        <v>79567</v>
+        <v>79637</v>
       </c>
       <c r="E108">
-        <v>96233</v>
+        <v>96295</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -2207,13 +2207,13 @@
         <v>50121</v>
       </c>
       <c r="C109">
-        <v>59425</v>
+        <v>59499</v>
       </c>
       <c r="D109">
-        <v>76561</v>
+        <v>76718</v>
       </c>
       <c r="E109">
-        <v>93557</v>
+        <v>93642</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -2224,13 +2224,13 @@
         <v>50121</v>
       </c>
       <c r="C110">
-        <v>59425</v>
+        <v>59499</v>
       </c>
       <c r="D110">
-        <v>76561</v>
+        <v>76718</v>
       </c>
       <c r="E110">
-        <v>93557</v>
+        <v>93642</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -2241,13 +2241,13 @@
         <v>50121</v>
       </c>
       <c r="C111">
-        <v>59425</v>
+        <v>59499</v>
       </c>
       <c r="D111">
-        <v>76561</v>
+        <v>76718</v>
       </c>
       <c r="E111">
-        <v>93557</v>
+        <v>93642</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -2255,16 +2255,16 @@
         <v>111</v>
       </c>
       <c r="B112">
-        <v>51220</v>
+        <v>51222</v>
       </c>
       <c r="C112">
-        <v>60783</v>
+        <v>60887</v>
       </c>
       <c r="D112">
-        <v>77802</v>
+        <v>77971</v>
       </c>
       <c r="E112">
-        <v>94464</v>
+        <v>94556</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -2275,13 +2275,13 @@
         <v>48853</v>
       </c>
       <c r="C113">
-        <v>58092</v>
+        <v>58147</v>
       </c>
       <c r="D113">
-        <v>75702</v>
+        <v>75863</v>
       </c>
       <c r="E113">
-        <v>93057</v>
+        <v>93149</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -2292,13 +2292,13 @@
         <v>49418</v>
       </c>
       <c r="C114">
-        <v>59122</v>
+        <v>59176</v>
       </c>
       <c r="D114">
-        <v>76925</v>
+        <v>77078</v>
       </c>
       <c r="E114">
-        <v>94058</v>
+        <v>94142</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -2306,16 +2306,16 @@
         <v>114</v>
       </c>
       <c r="B115">
-        <v>51220</v>
+        <v>51222</v>
       </c>
       <c r="C115">
-        <v>60783</v>
+        <v>60887</v>
       </c>
       <c r="D115">
-        <v>77802</v>
+        <v>77971</v>
       </c>
       <c r="E115">
-        <v>94464</v>
+        <v>94556</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -2323,16 +2323,16 @@
         <v>115</v>
       </c>
       <c r="B116">
-        <v>51220</v>
+        <v>51222</v>
       </c>
       <c r="C116">
-        <v>60783</v>
+        <v>60887</v>
       </c>
       <c r="D116">
-        <v>77802</v>
+        <v>77971</v>
       </c>
       <c r="E116">
-        <v>94464</v>
+        <v>94556</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -2343,13 +2343,13 @@
         <v>48853</v>
       </c>
       <c r="C117">
-        <v>58092</v>
+        <v>58147</v>
       </c>
       <c r="D117">
-        <v>75702</v>
+        <v>75863</v>
       </c>
       <c r="E117">
-        <v>93057</v>
+        <v>93149</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -2360,13 +2360,13 @@
         <v>50001</v>
       </c>
       <c r="C118">
-        <v>60164</v>
+        <v>60217</v>
       </c>
       <c r="D118">
-        <v>78127</v>
+        <v>78269</v>
       </c>
       <c r="E118">
-        <v>95005</v>
+        <v>95080</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -2377,13 +2377,13 @@
         <v>46892</v>
       </c>
       <c r="C119">
-        <v>55901</v>
+        <v>55929</v>
       </c>
       <c r="D119">
-        <v>73700</v>
+        <v>73852</v>
       </c>
       <c r="E119">
-        <v>91649</v>
+        <v>91728</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -2391,16 +2391,16 @@
         <v>119</v>
       </c>
       <c r="B120">
-        <v>53557</v>
+        <v>53558</v>
       </c>
       <c r="C120">
-        <v>62280</v>
+        <v>62296</v>
       </c>
       <c r="D120">
-        <v>78026</v>
+        <v>78145</v>
       </c>
       <c r="E120">
-        <v>94434</v>
+        <v>94509</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -2408,16 +2408,16 @@
         <v>120</v>
       </c>
       <c r="B121">
-        <v>53557</v>
+        <v>53558</v>
       </c>
       <c r="C121">
-        <v>62280</v>
+        <v>62296</v>
       </c>
       <c r="D121">
-        <v>78026</v>
+        <v>78145</v>
       </c>
       <c r="E121">
-        <v>94434</v>
+        <v>94509</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -2428,13 +2428,13 @@
         <v>51523</v>
       </c>
       <c r="C122">
-        <v>60611</v>
+        <v>60648</v>
       </c>
       <c r="D122">
-        <v>76974</v>
+        <v>77129</v>
       </c>
       <c r="E122">
-        <v>93612</v>
+        <v>93702</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -2445,13 +2445,13 @@
         <v>51523</v>
       </c>
       <c r="C123">
-        <v>60611</v>
+        <v>60648</v>
       </c>
       <c r="D123">
-        <v>76974</v>
+        <v>77129</v>
       </c>
       <c r="E123">
-        <v>93612</v>
+        <v>93702</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -2462,13 +2462,13 @@
         <v>51523</v>
       </c>
       <c r="C124">
-        <v>60611</v>
+        <v>60648</v>
       </c>
       <c r="D124">
-        <v>76974</v>
+        <v>77129</v>
       </c>
       <c r="E124">
-        <v>93612</v>
+        <v>93702</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -2479,13 +2479,13 @@
         <v>50835</v>
       </c>
       <c r="C125">
-        <v>60228</v>
+        <v>60274</v>
       </c>
       <c r="D125">
-        <v>76570</v>
+        <v>76781</v>
       </c>
       <c r="E125">
-        <v>92967</v>
+        <v>93080</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -2496,13 +2496,13 @@
         <v>51411</v>
       </c>
       <c r="C126">
-        <v>61273</v>
+        <v>61319</v>
       </c>
       <c r="D126">
-        <v>77788</v>
+        <v>77987</v>
       </c>
       <c r="E126">
-        <v>93984</v>
+        <v>94088</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -2510,16 +2510,16 @@
         <v>126</v>
       </c>
       <c r="B127">
-        <v>53819</v>
+        <v>53820</v>
       </c>
       <c r="C127">
-        <v>63896</v>
+        <v>63976</v>
       </c>
       <c r="D127">
-        <v>79890</v>
+        <v>80088</v>
       </c>
       <c r="E127">
-        <v>95657</v>
+        <v>95744</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -2530,13 +2530,13 @@
         <v>53208</v>
       </c>
       <c r="C128">
-        <v>62257</v>
+        <v>62295</v>
       </c>
       <c r="D128">
-        <v>77988</v>
+        <v>78102</v>
       </c>
       <c r="E128">
-        <v>94424</v>
+        <v>94497</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -2547,13 +2547,13 @@
         <v>53208</v>
       </c>
       <c r="C129">
-        <v>62257</v>
+        <v>62295</v>
       </c>
       <c r="D129">
-        <v>77988</v>
+        <v>78102</v>
       </c>
       <c r="E129">
-        <v>94424</v>
+        <v>94497</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -2564,13 +2564,13 @@
         <v>53996</v>
       </c>
       <c r="C130">
-        <v>61972</v>
+        <v>61991</v>
       </c>
       <c r="D130">
-        <v>76995</v>
+        <v>77075</v>
       </c>
       <c r="E130">
-        <v>93656</v>
+        <v>93714</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -2581,13 +2581,13 @@
         <v>53996</v>
       </c>
       <c r="C131">
-        <v>61972</v>
+        <v>61991</v>
       </c>
       <c r="D131">
-        <v>76995</v>
+        <v>77075</v>
       </c>
       <c r="E131">
-        <v>93656</v>
+        <v>93714</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -2598,13 +2598,13 @@
         <v>53996</v>
       </c>
       <c r="C132">
-        <v>61972</v>
+        <v>61991</v>
       </c>
       <c r="D132">
-        <v>76995</v>
+        <v>77075</v>
       </c>
       <c r="E132">
-        <v>93656</v>
+        <v>93714</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -2615,13 +2615,13 @@
         <v>53996</v>
       </c>
       <c r="C133">
-        <v>61972</v>
+        <v>61991</v>
       </c>
       <c r="D133">
-        <v>76995</v>
+        <v>77075</v>
       </c>
       <c r="E133">
-        <v>93656</v>
+        <v>93714</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -2632,13 +2632,13 @@
         <v>56130</v>
       </c>
       <c r="C134">
-        <v>64431</v>
+        <v>64446</v>
       </c>
       <c r="D134">
-        <v>78674</v>
+        <v>78731</v>
       </c>
       <c r="E134">
-        <v>94515</v>
+        <v>94564</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -2649,13 +2649,13 @@
         <v>53055</v>
       </c>
       <c r="C135">
-        <v>60903</v>
+        <v>60929</v>
       </c>
       <c r="D135">
-        <v>76026</v>
+        <v>76121</v>
       </c>
       <c r="E135">
-        <v>93001</v>
+        <v>93066</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -2663,16 +2663,16 @@
         <v>135</v>
       </c>
       <c r="B136">
-        <v>52084</v>
+        <v>52086</v>
       </c>
       <c r="C136">
-        <v>59836</v>
+        <v>59891</v>
       </c>
       <c r="D136">
-        <v>75338</v>
+        <v>75473</v>
       </c>
       <c r="E136">
-        <v>92544</v>
+        <v>92624</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -2680,16 +2680,16 @@
         <v>136</v>
       </c>
       <c r="B137">
-        <v>52084</v>
+        <v>52086</v>
       </c>
       <c r="C137">
-        <v>59836</v>
+        <v>59891</v>
       </c>
       <c r="D137">
-        <v>75338</v>
+        <v>75473</v>
       </c>
       <c r="E137">
-        <v>92544</v>
+        <v>92624</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -2697,16 +2697,16 @@
         <v>137</v>
       </c>
       <c r="B138">
-        <v>52084</v>
+        <v>52086</v>
       </c>
       <c r="C138">
-        <v>59836</v>
+        <v>59891</v>
       </c>
       <c r="D138">
-        <v>75338</v>
+        <v>75473</v>
       </c>
       <c r="E138">
-        <v>92544</v>
+        <v>92624</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -2717,13 +2717,13 @@
         <v>51934</v>
       </c>
       <c r="C139">
-        <v>59806</v>
+        <v>59849</v>
       </c>
       <c r="D139">
-        <v>75302</v>
+        <v>75426</v>
       </c>
       <c r="E139">
-        <v>92346</v>
+        <v>92420</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -2731,16 +2731,16 @@
         <v>139</v>
       </c>
       <c r="B140">
-        <v>48696</v>
+        <v>48699</v>
       </c>
       <c r="C140">
-        <v>57049</v>
+        <v>57117</v>
       </c>
       <c r="D140">
-        <v>73928</v>
+        <v>74093</v>
       </c>
       <c r="E140">
-        <v>92080</v>
+        <v>92176</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -2751,13 +2751,13 @@
         <v>51934</v>
       </c>
       <c r="C141">
-        <v>59806</v>
+        <v>59849</v>
       </c>
       <c r="D141">
-        <v>75302</v>
+        <v>75426</v>
       </c>
       <c r="E141">
-        <v>92346</v>
+        <v>92420</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -2768,13 +2768,13 @@
         <v>51934</v>
       </c>
       <c r="C142">
-        <v>59806</v>
+        <v>59849</v>
       </c>
       <c r="D142">
-        <v>75302</v>
+        <v>75426</v>
       </c>
       <c r="E142">
-        <v>92346</v>
+        <v>92420</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -2785,13 +2785,13 @@
         <v>52198</v>
       </c>
       <c r="C143">
-        <v>60442</v>
+        <v>60480</v>
       </c>
       <c r="D143">
-        <v>75796</v>
+        <v>75925</v>
       </c>
       <c r="E143">
-        <v>92500</v>
+        <v>92587</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -2802,13 +2802,13 @@
         <v>52198</v>
       </c>
       <c r="C144">
-        <v>60442</v>
+        <v>60480</v>
       </c>
       <c r="D144">
-        <v>75796</v>
+        <v>75925</v>
       </c>
       <c r="E144">
-        <v>92500</v>
+        <v>92587</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -2819,13 +2819,13 @@
         <v>52198</v>
       </c>
       <c r="C145">
-        <v>60442</v>
+        <v>60480</v>
       </c>
       <c r="D145">
-        <v>75796</v>
+        <v>75925</v>
       </c>
       <c r="E145">
-        <v>92500</v>
+        <v>92587</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -2836,13 +2836,13 @@
         <v>53208</v>
       </c>
       <c r="C146">
-        <v>62257</v>
+        <v>62295</v>
       </c>
       <c r="D146">
-        <v>77988</v>
+        <v>78102</v>
       </c>
       <c r="E146">
-        <v>94424</v>
+        <v>94497</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -2853,13 +2853,13 @@
         <v>49843</v>
       </c>
       <c r="C147">
-        <v>57397</v>
+        <v>57442</v>
       </c>
       <c r="D147">
-        <v>73252</v>
+        <v>73380</v>
       </c>
       <c r="E147">
-        <v>91061</v>
+        <v>91149</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -2870,13 +2870,13 @@
         <v>49404</v>
       </c>
       <c r="C148">
-        <v>56596</v>
+        <v>56640</v>
       </c>
       <c r="D148">
-        <v>72161</v>
+        <v>72297</v>
       </c>
       <c r="E148">
-        <v>90014</v>
+        <v>90108</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -2887,13 +2887,13 @@
         <v>47901</v>
       </c>
       <c r="C149">
-        <v>54613</v>
+        <v>54628</v>
       </c>
       <c r="D149">
-        <v>69592</v>
+        <v>69652</v>
       </c>
       <c r="E149">
-        <v>87456</v>
+        <v>87524</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -2904,13 +2904,13 @@
         <v>47901</v>
       </c>
       <c r="C150">
-        <v>54613</v>
+        <v>54628</v>
       </c>
       <c r="D150">
-        <v>69592</v>
+        <v>69652</v>
       </c>
       <c r="E150">
-        <v>87456</v>
+        <v>87524</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -2921,13 +2921,13 @@
         <v>47901</v>
       </c>
       <c r="C151">
-        <v>54613</v>
+        <v>54628</v>
       </c>
       <c r="D151">
-        <v>69592</v>
+        <v>69652</v>
       </c>
       <c r="E151">
-        <v>87456</v>
+        <v>87524</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -2938,13 +2938,13 @@
         <v>47901</v>
       </c>
       <c r="C152">
-        <v>54613</v>
+        <v>54628</v>
       </c>
       <c r="D152">
-        <v>69592</v>
+        <v>69652</v>
       </c>
       <c r="E152">
-        <v>87456</v>
+        <v>87524</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -2955,13 +2955,13 @@
         <v>45061</v>
       </c>
       <c r="C153">
-        <v>52904</v>
+        <v>52978</v>
       </c>
       <c r="D153">
-        <v>70083</v>
+        <v>70272</v>
       </c>
       <c r="E153">
-        <v>89103</v>
+        <v>89225</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -2972,13 +2972,13 @@
         <v>45061</v>
       </c>
       <c r="C154">
-        <v>52904</v>
+        <v>52978</v>
       </c>
       <c r="D154">
-        <v>70083</v>
+        <v>70272</v>
       </c>
       <c r="E154">
-        <v>89103</v>
+        <v>89225</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -2989,13 +2989,13 @@
         <v>42515</v>
       </c>
       <c r="C155">
-        <v>49052</v>
+        <v>49083</v>
       </c>
       <c r="D155">
-        <v>64927</v>
+        <v>65134</v>
       </c>
       <c r="E155">
-        <v>84091</v>
+        <v>84241</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -3006,13 +3006,13 @@
         <v>42515</v>
       </c>
       <c r="C156">
-        <v>49052</v>
+        <v>49083</v>
       </c>
       <c r="D156">
-        <v>64927</v>
+        <v>65134</v>
       </c>
       <c r="E156">
-        <v>84091</v>
+        <v>84241</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -3023,13 +3023,13 @@
         <v>42914</v>
       </c>
       <c r="C157">
-        <v>49775</v>
+        <v>49806</v>
       </c>
       <c r="D157">
-        <v>65991</v>
+        <v>66189</v>
       </c>
       <c r="E157">
-        <v>85241</v>
+        <v>85383</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -3040,13 +3040,13 @@
         <v>45613</v>
       </c>
       <c r="C158">
-        <v>52825</v>
+        <v>52858</v>
       </c>
       <c r="D158">
-        <v>68704</v>
+        <v>68812</v>
       </c>
       <c r="E158">
-        <v>87183</v>
+        <v>87284</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -3057,13 +3057,13 @@
         <v>45192</v>
       </c>
       <c r="C159">
-        <v>52055</v>
+        <v>52088</v>
       </c>
       <c r="D159">
-        <v>67615</v>
+        <v>67725</v>
       </c>
       <c r="E159">
-        <v>86035</v>
+        <v>86141</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -3074,13 +3074,13 @@
         <v>42201</v>
       </c>
       <c r="C160">
-        <v>48836</v>
+        <v>48855</v>
       </c>
       <c r="D160">
-        <v>64565</v>
+        <v>64710</v>
       </c>
       <c r="E160">
-        <v>83646</v>
+        <v>83772</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -3088,16 +3088,16 @@
         <v>160</v>
       </c>
       <c r="B161">
-        <v>42478</v>
+        <v>42484</v>
       </c>
       <c r="C161">
-        <v>50747</v>
+        <v>50851</v>
       </c>
       <c r="D161">
-        <v>68369</v>
+        <v>68579</v>
       </c>
       <c r="E161">
-        <v>87647</v>
+        <v>87791</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -3108,13 +3108,13 @@
         <v>43046</v>
       </c>
       <c r="C162">
-        <v>50303</v>
+        <v>50322</v>
       </c>
       <c r="D162">
-        <v>66676</v>
+        <v>66806</v>
       </c>
       <c r="E162">
-        <v>85929</v>
+        <v>86042</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -3125,13 +3125,13 @@
         <v>48548</v>
       </c>
       <c r="C163">
-        <v>55585</v>
+        <v>55609</v>
       </c>
       <c r="D163">
-        <v>70602</v>
+        <v>70729</v>
       </c>
       <c r="E163">
-        <v>88372</v>
+        <v>88469</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -3142,13 +3142,13 @@
         <v>48975</v>
       </c>
       <c r="C164">
-        <v>56349</v>
+        <v>56373</v>
       </c>
       <c r="D164">
-        <v>71662</v>
+        <v>71785</v>
       </c>
       <c r="E164">
-        <v>89444</v>
+        <v>89536</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -3159,13 +3159,13 @@
         <v>44961</v>
       </c>
       <c r="C165">
-        <v>52176</v>
+        <v>52213</v>
       </c>
       <c r="D165">
-        <v>67988</v>
+        <v>68160</v>
       </c>
       <c r="E165">
-        <v>86316</v>
+        <v>86440</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -3176,13 +3176,13 @@
         <v>44961</v>
       </c>
       <c r="C166">
-        <v>52176</v>
+        <v>52213</v>
       </c>
       <c r="D166">
-        <v>67988</v>
+        <v>68160</v>
       </c>
       <c r="E166">
-        <v>86316</v>
+        <v>86440</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -3193,13 +3193,13 @@
         <v>44553</v>
       </c>
       <c r="C167">
-        <v>53071</v>
+        <v>53152</v>
       </c>
       <c r="D167">
-        <v>70602</v>
+        <v>70779</v>
       </c>
       <c r="E167">
-        <v>89485</v>
+        <v>89593</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -3210,13 +3210,13 @@
         <v>45039</v>
       </c>
       <c r="C168">
-        <v>53939</v>
+        <v>54019</v>
       </c>
       <c r="D168">
-        <v>71758</v>
+        <v>71923</v>
       </c>
       <c r="E168">
-        <v>90561</v>
+        <v>90661</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -3227,13 +3227,13 @@
         <v>54013</v>
       </c>
       <c r="C169">
-        <v>62280</v>
+        <v>62296</v>
       </c>
       <c r="D169">
-        <v>77722</v>
+        <v>77829</v>
       </c>
       <c r="E169">
-        <v>94424</v>
+        <v>94489</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -3244,13 +3244,13 @@
         <v>52419</v>
       </c>
       <c r="C170">
-        <v>59977</v>
+        <v>59982</v>
       </c>
       <c r="D170">
-        <v>75552</v>
+        <v>75627</v>
       </c>
       <c r="E170">
-        <v>93017</v>
+        <v>93078</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -3261,13 +3261,13 @@
         <v>54013</v>
       </c>
       <c r="C171">
-        <v>62280</v>
+        <v>62296</v>
       </c>
       <c r="D171">
-        <v>77722</v>
+        <v>77829</v>
       </c>
       <c r="E171">
-        <v>94424</v>
+        <v>94489</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -3278,13 +3278,13 @@
         <v>52419</v>
       </c>
       <c r="C172">
-        <v>59977</v>
+        <v>59982</v>
       </c>
       <c r="D172">
-        <v>75552</v>
+        <v>75627</v>
       </c>
       <c r="E172">
-        <v>93017</v>
+        <v>93078</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -3295,13 +3295,13 @@
         <v>52419</v>
       </c>
       <c r="C173">
-        <v>59977</v>
+        <v>59982</v>
       </c>
       <c r="D173">
-        <v>75552</v>
+        <v>75627</v>
       </c>
       <c r="E173">
-        <v>93017</v>
+        <v>93078</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -3312,13 +3312,13 @@
         <v>53157</v>
       </c>
       <c r="C174">
-        <v>60696</v>
+        <v>60702</v>
       </c>
       <c r="D174">
-        <v>75587</v>
+        <v>75638</v>
       </c>
       <c r="E174">
-        <v>92624</v>
+        <v>92672</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -3326,16 +3326,16 @@
         <v>174</v>
       </c>
       <c r="B175">
-        <v>52262</v>
+        <v>52264</v>
       </c>
       <c r="C175">
-        <v>60974</v>
+        <v>61008</v>
       </c>
       <c r="D175">
-        <v>77567</v>
+        <v>77688</v>
       </c>
       <c r="E175">
-        <v>94926</v>
+        <v>94993</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -3343,16 +3343,16 @@
         <v>175</v>
       </c>
       <c r="B176">
-        <v>51752</v>
+        <v>51754</v>
       </c>
       <c r="C176">
-        <v>60096</v>
+        <v>60131</v>
       </c>
       <c r="D176">
-        <v>76486</v>
+        <v>76615</v>
       </c>
       <c r="E176">
-        <v>94012</v>
+        <v>94087</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -3360,16 +3360,16 @@
         <v>176</v>
       </c>
       <c r="B177">
-        <v>51752</v>
+        <v>51754</v>
       </c>
       <c r="C177">
-        <v>60096</v>
+        <v>60131</v>
       </c>
       <c r="D177">
-        <v>76486</v>
+        <v>76615</v>
       </c>
       <c r="E177">
-        <v>94012</v>
+        <v>94087</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -3380,13 +3380,13 @@
         <v>51815</v>
       </c>
       <c r="C178">
-        <v>59554</v>
+        <v>59575</v>
       </c>
       <c r="D178">
-        <v>75286</v>
+        <v>75389</v>
       </c>
       <c r="E178">
-        <v>92775</v>
+        <v>92847</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -3397,13 +3397,13 @@
         <v>51218</v>
       </c>
       <c r="C179">
-        <v>59104</v>
+        <v>59141</v>
       </c>
       <c r="D179">
-        <v>75092</v>
+        <v>75202</v>
       </c>
       <c r="E179">
-        <v>92708</v>
+        <v>92780</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -3414,13 +3414,13 @@
         <v>52208</v>
       </c>
       <c r="C180">
-        <v>60847</v>
+        <v>60882</v>
       </c>
       <c r="D180">
-        <v>77269</v>
+        <v>77367</v>
       </c>
       <c r="E180">
-        <v>94617</v>
+        <v>94675</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -3431,13 +3431,13 @@
         <v>52208</v>
       </c>
       <c r="C181">
-        <v>60847</v>
+        <v>60882</v>
       </c>
       <c r="D181">
-        <v>77269</v>
+        <v>77367</v>
       </c>
       <c r="E181">
-        <v>94617</v>
+        <v>94675</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -3445,16 +3445,16 @@
         <v>181</v>
       </c>
       <c r="B182">
-        <v>44705</v>
+        <v>44707</v>
       </c>
       <c r="C182">
-        <v>52498</v>
+        <v>52578</v>
       </c>
       <c r="D182">
-        <v>70069</v>
+        <v>70263</v>
       </c>
       <c r="E182">
-        <v>89586</v>
+        <v>89718</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -3465,13 +3465,13 @@
         <v>43319</v>
       </c>
       <c r="C183">
-        <v>50316</v>
+        <v>50327</v>
       </c>
       <c r="D183">
-        <v>67817</v>
+        <v>68000</v>
       </c>
       <c r="E183">
-        <v>87794</v>
+        <v>87959</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -3482,13 +3482,13 @@
         <v>48316</v>
       </c>
       <c r="C184">
-        <v>56636</v>
+        <v>56648</v>
       </c>
       <c r="D184">
-        <v>73649</v>
+        <v>73771</v>
       </c>
       <c r="E184">
-        <v>92138</v>
+        <v>92221</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -3499,13 +3499,13 @@
         <v>48316</v>
       </c>
       <c r="C185">
-        <v>56636</v>
+        <v>56648</v>
       </c>
       <c r="D185">
-        <v>73649</v>
+        <v>73771</v>
       </c>
       <c r="E185">
-        <v>92138</v>
+        <v>92221</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -3516,13 +3516,13 @@
         <v>45007</v>
       </c>
       <c r="C186">
-        <v>53058</v>
+        <v>53066</v>
       </c>
       <c r="D186">
-        <v>70762</v>
+        <v>70846</v>
       </c>
       <c r="E186">
-        <v>90022</v>
+        <v>90100</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -3533,13 +3533,13 @@
         <v>44551</v>
       </c>
       <c r="C187">
-        <v>52194</v>
+        <v>52202</v>
       </c>
       <c r="D187">
-        <v>69624</v>
+        <v>69711</v>
       </c>
       <c r="E187">
-        <v>88937</v>
+        <v>89021</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -3550,13 +3550,13 @@
         <v>44162</v>
       </c>
       <c r="C188">
-        <v>52236</v>
+        <v>52298</v>
       </c>
       <c r="D188">
-        <v>70196</v>
+        <v>70430</v>
       </c>
       <c r="E188">
-        <v>89844</v>
+        <v>89985</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -3567,13 +3567,13 @@
         <v>44162</v>
       </c>
       <c r="C189">
-        <v>52236</v>
+        <v>52298</v>
       </c>
       <c r="D189">
-        <v>70196</v>
+        <v>70430</v>
       </c>
       <c r="E189">
-        <v>89844</v>
+        <v>89985</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -3584,13 +3584,13 @@
         <v>44162</v>
       </c>
       <c r="C190">
-        <v>52236</v>
+        <v>52298</v>
       </c>
       <c r="D190">
-        <v>70196</v>
+        <v>70430</v>
       </c>
       <c r="E190">
-        <v>89844</v>
+        <v>89985</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -3601,13 +3601,13 @@
         <v>48299</v>
       </c>
       <c r="C191">
-        <v>56874</v>
+        <v>56903</v>
       </c>
       <c r="D191">
-        <v>74007</v>
+        <v>74149</v>
       </c>
       <c r="E191">
-        <v>92356</v>
+        <v>92445</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -3618,13 +3618,13 @@
         <v>44551</v>
       </c>
       <c r="C192">
-        <v>52194</v>
+        <v>52202</v>
       </c>
       <c r="D192">
-        <v>69624</v>
+        <v>69711</v>
       </c>
       <c r="E192">
-        <v>88937</v>
+        <v>89021</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -3635,13 +3635,13 @@
         <v>53168</v>
       </c>
       <c r="C193">
-        <v>61438</v>
+        <v>61453</v>
       </c>
       <c r="D193">
-        <v>77377</v>
+        <v>77464</v>
       </c>
       <c r="E193">
-        <v>94188</v>
+        <v>94256</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -3652,13 +3652,13 @@
         <v>53168</v>
       </c>
       <c r="C194">
-        <v>61438</v>
+        <v>61453</v>
       </c>
       <c r="D194">
-        <v>77377</v>
+        <v>77464</v>
       </c>
       <c r="E194">
-        <v>94188</v>
+        <v>94256</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -3669,13 +3669,13 @@
         <v>54013</v>
       </c>
       <c r="C195">
-        <v>62280</v>
+        <v>62296</v>
       </c>
       <c r="D195">
-        <v>77722</v>
+        <v>77829</v>
       </c>
       <c r="E195">
-        <v>94424</v>
+        <v>94489</v>
       </c>
     </row>
     <row r="196" spans="1:5">
@@ -3686,13 +3686,13 @@
         <v>49493</v>
       </c>
       <c r="C196">
-        <v>57412</v>
+        <v>57426</v>
       </c>
       <c r="D196">
-        <v>73939</v>
+        <v>74060</v>
       </c>
       <c r="E196">
-        <v>91950</v>
+        <v>92031</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -3703,13 +3703,13 @@
         <v>49791</v>
       </c>
       <c r="C197">
-        <v>57817</v>
+        <v>57842</v>
       </c>
       <c r="D197">
-        <v>74584</v>
+        <v>74713</v>
       </c>
       <c r="E197">
-        <v>92389</v>
+        <v>92474</v>
       </c>
     </row>
     <row r="198" spans="1:5">
@@ -3720,13 +3720,13 @@
         <v>49791</v>
       </c>
       <c r="C198">
-        <v>57817</v>
+        <v>57842</v>
       </c>
       <c r="D198">
-        <v>74584</v>
+        <v>74713</v>
       </c>
       <c r="E198">
-        <v>92389</v>
+        <v>92474</v>
       </c>
     </row>
     <row r="199" spans="1:5">
@@ -3737,13 +3737,13 @@
         <v>50289</v>
       </c>
       <c r="C199">
-        <v>58753</v>
+        <v>58777</v>
       </c>
       <c r="D199">
-        <v>75757</v>
+        <v>75880</v>
       </c>
       <c r="E199">
-        <v>93394</v>
+        <v>93472</v>
       </c>
     </row>
     <row r="200" spans="1:5">
@@ -3754,13 +3754,13 @@
         <v>50289</v>
       </c>
       <c r="C200">
-        <v>58753</v>
+        <v>58777</v>
       </c>
       <c r="D200">
-        <v>75757</v>
+        <v>75880</v>
       </c>
       <c r="E200">
-        <v>93394</v>
+        <v>93472</v>
       </c>
     </row>
     <row r="201" spans="1:5">
@@ -3771,13 +3771,13 @@
         <v>51379</v>
       </c>
       <c r="C201">
-        <v>60914</v>
+        <v>60915</v>
       </c>
       <c r="D201">
-        <v>78421</v>
+        <v>78495</v>
       </c>
       <c r="E201">
-        <v>95355</v>
+        <v>95425</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -3788,13 +3788,13 @@
         <v>48907</v>
       </c>
       <c r="C202">
-        <v>58712</v>
+        <v>58732</v>
       </c>
       <c r="D202">
-        <v>77086</v>
+        <v>77223</v>
       </c>
       <c r="E202">
-        <v>94767</v>
+        <v>94852</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -3805,13 +3805,13 @@
         <v>49980</v>
       </c>
       <c r="C203">
-        <v>58305</v>
+        <v>58318</v>
       </c>
       <c r="D203">
-        <v>75037</v>
+        <v>75153</v>
       </c>
       <c r="E203">
-        <v>92936</v>
+        <v>93012</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -3822,13 +3822,13 @@
         <v>47863</v>
       </c>
       <c r="C204">
-        <v>56376</v>
+        <v>56395</v>
       </c>
       <c r="D204">
-        <v>73819</v>
+        <v>73966</v>
       </c>
       <c r="E204">
-        <v>92143</v>
+        <v>92228</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -3839,13 +3839,13 @@
         <v>48372</v>
       </c>
       <c r="C205">
-        <v>57296</v>
+        <v>57315</v>
       </c>
       <c r="D205">
-        <v>74943</v>
+        <v>75084</v>
       </c>
       <c r="E205">
-        <v>93124</v>
+        <v>93202</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -3856,13 +3856,13 @@
         <v>35637</v>
       </c>
       <c r="C206">
-        <v>45909</v>
+        <v>45922</v>
       </c>
       <c r="D206">
-        <v>62274</v>
+        <v>62410</v>
       </c>
       <c r="E206">
-        <v>79068</v>
+        <v>79383</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -3870,16 +3870,16 @@
         <v>206</v>
       </c>
       <c r="B207">
-        <v>31585</v>
+        <v>31586</v>
       </c>
       <c r="C207">
-        <v>40958</v>
+        <v>40970</v>
       </c>
       <c r="D207">
-        <v>57060</v>
+        <v>57252</v>
       </c>
       <c r="E207">
-        <v>73925</v>
+        <v>74440</v>
       </c>
     </row>
     <row r="208" spans="1:5">
@@ -3887,16 +3887,16 @@
         <v>207</v>
       </c>
       <c r="B208">
-        <v>31585</v>
+        <v>31586</v>
       </c>
       <c r="C208">
-        <v>40958</v>
+        <v>40970</v>
       </c>
       <c r="D208">
-        <v>57060</v>
+        <v>57252</v>
       </c>
       <c r="E208">
-        <v>73925</v>
+        <v>74440</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -3907,13 +3907,13 @@
         <v>35637</v>
       </c>
       <c r="C209">
-        <v>45909</v>
+        <v>45922</v>
       </c>
       <c r="D209">
-        <v>62274</v>
+        <v>62410</v>
       </c>
       <c r="E209">
-        <v>79068</v>
+        <v>79383</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -3921,16 +3921,16 @@
         <v>209</v>
       </c>
       <c r="B210">
-        <v>31585</v>
+        <v>31586</v>
       </c>
       <c r="C210">
-        <v>40958</v>
+        <v>40970</v>
       </c>
       <c r="D210">
-        <v>57060</v>
+        <v>57252</v>
       </c>
       <c r="E210">
-        <v>73925</v>
+        <v>74440</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -3941,13 +3941,13 @@
         <v>32413</v>
       </c>
       <c r="C211">
-        <v>41947</v>
+        <v>41961</v>
       </c>
       <c r="D211">
-        <v>58430</v>
+        <v>58549</v>
       </c>
       <c r="E211">
-        <v>75997</v>
+        <v>76414</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -3955,16 +3955,16 @@
         <v>211</v>
       </c>
       <c r="B212">
-        <v>35027</v>
+        <v>35028</v>
       </c>
       <c r="C212">
-        <v>45635</v>
+        <v>45658</v>
       </c>
       <c r="D212">
-        <v>62997</v>
+        <v>63367</v>
       </c>
       <c r="E212">
-        <v>80609</v>
+        <v>81184</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -3972,16 +3972,16 @@
         <v>212</v>
       </c>
       <c r="B213">
-        <v>31585</v>
+        <v>31586</v>
       </c>
       <c r="C213">
-        <v>40958</v>
+        <v>40970</v>
       </c>
       <c r="D213">
-        <v>57060</v>
+        <v>57252</v>
       </c>
       <c r="E213">
-        <v>73925</v>
+        <v>74440</v>
       </c>
     </row>
     <row r="214" spans="1:5">
@@ -3992,13 +3992,13 @@
         <v>29083</v>
       </c>
       <c r="C214">
-        <v>37464</v>
+        <v>37466</v>
       </c>
       <c r="D214">
-        <v>53041</v>
+        <v>53132</v>
       </c>
       <c r="E214">
-        <v>69878</v>
+        <v>70279</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -4009,13 +4009,13 @@
         <v>29083</v>
       </c>
       <c r="C215">
-        <v>37464</v>
+        <v>37466</v>
       </c>
       <c r="D215">
-        <v>53041</v>
+        <v>53132</v>
       </c>
       <c r="E215">
-        <v>69878</v>
+        <v>70279</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -4026,13 +4026,13 @@
         <v>28328</v>
       </c>
       <c r="C216">
-        <v>36389</v>
+        <v>36393</v>
       </c>
       <c r="D216">
-        <v>51479</v>
+        <v>51589</v>
       </c>
       <c r="E216">
-        <v>68084</v>
+        <v>68528</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -4043,13 +4043,13 @@
         <v>29338</v>
       </c>
       <c r="C217">
-        <v>38114</v>
+        <v>38120</v>
       </c>
       <c r="D217">
-        <v>54184</v>
+        <v>54325</v>
       </c>
       <c r="E217">
-        <v>71310</v>
+        <v>71786</v>
       </c>
     </row>
     <row r="218" spans="1:5">
@@ -4060,13 +4060,13 @@
         <v>29714</v>
       </c>
       <c r="C218">
-        <v>38909</v>
+        <v>38914</v>
       </c>
       <c r="D218">
-        <v>55478</v>
+        <v>55615</v>
       </c>
       <c r="E218">
-        <v>72963</v>
+        <v>73423</v>
       </c>
     </row>
     <row r="219" spans="1:5">
@@ -4077,13 +4077,13 @@
         <v>35199</v>
       </c>
       <c r="C219">
-        <v>45332</v>
+        <v>45341</v>
       </c>
       <c r="D219">
-        <v>62572</v>
+        <v>62745</v>
       </c>
       <c r="E219">
-        <v>80106</v>
+        <v>80492</v>
       </c>
     </row>
     <row r="220" spans="1:5">
@@ -4091,16 +4091,16 @@
         <v>219</v>
       </c>
       <c r="B220">
-        <v>35220</v>
+        <v>35221</v>
       </c>
       <c r="C220">
-        <v>46696</v>
+        <v>46757</v>
       </c>
       <c r="D220">
-        <v>64726</v>
+        <v>65197</v>
       </c>
       <c r="E220">
-        <v>82401</v>
+        <v>82954</v>
       </c>
     </row>
     <row r="221" spans="1:5">
@@ -4111,13 +4111,13 @@
         <v>37882</v>
       </c>
       <c r="C221">
-        <v>48364</v>
+        <v>48370</v>
       </c>
       <c r="D221">
-        <v>65858</v>
+        <v>65984</v>
       </c>
       <c r="E221">
-        <v>83320</v>
+        <v>83545</v>
       </c>
     </row>
     <row r="222" spans="1:5">
@@ -4128,13 +4128,13 @@
         <v>35199</v>
       </c>
       <c r="C222">
-        <v>45332</v>
+        <v>45341</v>
       </c>
       <c r="D222">
-        <v>62572</v>
+        <v>62745</v>
       </c>
       <c r="E222">
-        <v>80106</v>
+        <v>80492</v>
       </c>
     </row>
     <row r="223" spans="1:5">
@@ -4145,13 +4145,13 @@
         <v>38414</v>
       </c>
       <c r="C223">
-        <v>49401</v>
+        <v>49407</v>
       </c>
       <c r="D223">
-        <v>67204</v>
+        <v>67324</v>
       </c>
       <c r="E223">
-        <v>84701</v>
+        <v>84915</v>
       </c>
     </row>
     <row r="224" spans="1:5">
@@ -4165,10 +4165,10 @@
         <v>37679</v>
       </c>
       <c r="D224">
-        <v>53277</v>
+        <v>53289</v>
       </c>
       <c r="E224">
-        <v>70473</v>
+        <v>70577</v>
       </c>
     </row>
     <row r="225" spans="1:5">
@@ -4182,10 +4182,10 @@
         <v>36397</v>
       </c>
       <c r="D225">
-        <v>51016</v>
+        <v>51032</v>
       </c>
       <c r="E225">
-        <v>67219</v>
+        <v>67331</v>
       </c>
     </row>
     <row r="226" spans="1:5">
@@ -4199,10 +4199,10 @@
         <v>37031</v>
       </c>
       <c r="D226">
-        <v>52139</v>
+        <v>52154</v>
       </c>
       <c r="E226">
-        <v>68854</v>
+        <v>68963</v>
       </c>
     </row>
     <row r="227" spans="1:5">
@@ -4213,13 +4213,13 @@
         <v>29342</v>
       </c>
       <c r="C227">
-        <v>37018</v>
+        <v>37021</v>
       </c>
       <c r="D227">
-        <v>51204</v>
+        <v>51230</v>
       </c>
       <c r="E227">
-        <v>67192</v>
+        <v>67294</v>
       </c>
     </row>
     <row r="228" spans="1:5">
@@ -4230,13 +4230,13 @@
         <v>25742</v>
       </c>
       <c r="C228">
-        <v>34302</v>
+        <v>34305</v>
       </c>
       <c r="D228">
-        <v>51363</v>
+        <v>51421</v>
       </c>
       <c r="E228">
-        <v>70175</v>
+        <v>70488</v>
       </c>
     </row>
     <row r="229" spans="1:5">
@@ -4244,16 +4244,16 @@
         <v>228</v>
       </c>
       <c r="B229">
-        <v>35220</v>
+        <v>35221</v>
       </c>
       <c r="C229">
-        <v>46696</v>
+        <v>46757</v>
       </c>
       <c r="D229">
-        <v>64726</v>
+        <v>65197</v>
       </c>
       <c r="E229">
-        <v>82401</v>
+        <v>82954</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -4264,13 +4264,13 @@
         <v>37366</v>
       </c>
       <c r="C230">
-        <v>47363</v>
+        <v>47369</v>
       </c>
       <c r="D230">
-        <v>64507</v>
+        <v>64638</v>
       </c>
       <c r="E230">
-        <v>81885</v>
+        <v>82118</v>
       </c>
     </row>
     <row r="231" spans="1:5">
@@ -4278,16 +4278,16 @@
         <v>230</v>
       </c>
       <c r="B231">
-        <v>35520</v>
+        <v>35521</v>
       </c>
       <c r="C231">
-        <v>46624</v>
+        <v>46646</v>
       </c>
       <c r="D231">
-        <v>64337</v>
+        <v>64697</v>
       </c>
       <c r="E231">
-        <v>82072</v>
+        <v>82616</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -4298,13 +4298,13 @@
         <v>31937</v>
       </c>
       <c r="C232">
-        <v>41676</v>
+        <v>41687</v>
       </c>
       <c r="D232">
-        <v>59154</v>
+        <v>59401</v>
       </c>
       <c r="E232">
-        <v>77251</v>
+        <v>77824</v>
       </c>
     </row>
     <row r="233" spans="1:5">
@@ -4315,13 +4315,13 @@
         <v>32364</v>
       </c>
       <c r="C233">
-        <v>42610</v>
+        <v>42620</v>
       </c>
       <c r="D233">
-        <v>60540</v>
+        <v>60780</v>
       </c>
       <c r="E233">
-        <v>78839</v>
+        <v>79379</v>
       </c>
     </row>
     <row r="234" spans="1:5">
@@ -4332,13 +4332,13 @@
         <v>37264</v>
       </c>
       <c r="C234">
-        <v>47722</v>
+        <v>47725</v>
       </c>
       <c r="D234">
-        <v>64795</v>
+        <v>64969</v>
       </c>
       <c r="E234">
-        <v>82105</v>
+        <v>82515</v>
       </c>
     </row>
     <row r="235" spans="1:5">
@@ -4349,13 +4349,13 @@
         <v>37264</v>
       </c>
       <c r="C235">
-        <v>47722</v>
+        <v>47725</v>
       </c>
       <c r="D235">
-        <v>64795</v>
+        <v>64969</v>
       </c>
       <c r="E235">
-        <v>82105</v>
+        <v>82515</v>
       </c>
     </row>
     <row r="236" spans="1:5">
@@ -4366,13 +4366,13 @@
         <v>37264</v>
       </c>
       <c r="C236">
-        <v>47722</v>
+        <v>47725</v>
       </c>
       <c r="D236">
-        <v>64795</v>
+        <v>64969</v>
       </c>
       <c r="E236">
-        <v>82105</v>
+        <v>82515</v>
       </c>
     </row>
     <row r="237" spans="1:5">
@@ -4383,13 +4383,13 @@
         <v>29655</v>
       </c>
       <c r="C237">
-        <v>37605</v>
+        <v>37607</v>
       </c>
       <c r="D237">
-        <v>52305</v>
+        <v>52327</v>
       </c>
       <c r="E237">
-        <v>68799</v>
+        <v>68896</v>
       </c>
     </row>
     <row r="238" spans="1:5">
@@ -4400,13 +4400,13 @@
         <v>29342</v>
       </c>
       <c r="C238">
-        <v>37018</v>
+        <v>37021</v>
       </c>
       <c r="D238">
-        <v>51204</v>
+        <v>51230</v>
       </c>
       <c r="E238">
-        <v>67192</v>
+        <v>67294</v>
       </c>
     </row>
     <row r="239" spans="1:5">
@@ -4417,13 +4417,13 @@
         <v>29971</v>
       </c>
       <c r="C239">
-        <v>38215</v>
+        <v>38217</v>
       </c>
       <c r="D239">
-        <v>53435</v>
+        <v>53453</v>
       </c>
       <c r="E239">
-        <v>70396</v>
+        <v>70488</v>
       </c>
     </row>
     <row r="240" spans="1:5">
@@ -4434,13 +4434,13 @@
         <v>27222</v>
       </c>
       <c r="C240">
-        <v>35377</v>
+        <v>35381</v>
       </c>
       <c r="D240">
-        <v>50801</v>
+        <v>50905</v>
       </c>
       <c r="E240">
-        <v>67754</v>
+        <v>68134</v>
       </c>
     </row>
     <row r="241" spans="1:5">
@@ -4451,13 +4451,13 @@
         <v>27073</v>
       </c>
       <c r="C241">
-        <v>35137</v>
+        <v>35139</v>
       </c>
       <c r="D241">
-        <v>50420</v>
+        <v>50467</v>
       </c>
       <c r="E241">
-        <v>67259</v>
+        <v>67545</v>
       </c>
     </row>
     <row r="242" spans="1:5">
@@ -4468,13 +4468,13 @@
         <v>37882</v>
       </c>
       <c r="C242">
-        <v>48364</v>
+        <v>48370</v>
       </c>
       <c r="D242">
-        <v>65858</v>
+        <v>65984</v>
       </c>
       <c r="E242">
-        <v>83320</v>
+        <v>83545</v>
       </c>
     </row>
     <row r="243" spans="1:5">
@@ -4485,13 +4485,13 @@
         <v>39916</v>
       </c>
       <c r="C243">
-        <v>50540</v>
+        <v>50557</v>
       </c>
       <c r="D243">
-        <v>67860</v>
+        <v>68039</v>
       </c>
       <c r="E243">
-        <v>85016</v>
+        <v>85247</v>
       </c>
     </row>
     <row r="244" spans="1:5">
@@ -4502,13 +4502,13 @@
         <v>37882</v>
       </c>
       <c r="C244">
-        <v>48364</v>
+        <v>48370</v>
       </c>
       <c r="D244">
-        <v>65858</v>
+        <v>65984</v>
       </c>
       <c r="E244">
-        <v>83320</v>
+        <v>83545</v>
       </c>
     </row>
     <row r="245" spans="1:5">
@@ -4519,13 +4519,13 @@
         <v>40496</v>
       </c>
       <c r="C245">
-        <v>51632</v>
+        <v>51649</v>
       </c>
       <c r="D245">
-        <v>69231</v>
+        <v>69403</v>
       </c>
       <c r="E245">
-        <v>86338</v>
+        <v>86558</v>
       </c>
     </row>
     <row r="246" spans="1:5">
@@ -4536,13 +4536,13 @@
         <v>41858</v>
       </c>
       <c r="C246">
-        <v>53857</v>
+        <v>53865</v>
       </c>
       <c r="D246">
-        <v>71449</v>
+        <v>71596</v>
       </c>
       <c r="E246">
-        <v>88266</v>
+        <v>88437</v>
       </c>
     </row>
     <row r="247" spans="1:5">
@@ -4553,13 +4553,13 @@
         <v>41858</v>
       </c>
       <c r="C247">
-        <v>53857</v>
+        <v>53865</v>
       </c>
       <c r="D247">
-        <v>71449</v>
+        <v>71596</v>
       </c>
       <c r="E247">
-        <v>88266</v>
+        <v>88437</v>
       </c>
     </row>
     <row r="248" spans="1:5">
@@ -4570,13 +4570,13 @@
         <v>33261</v>
       </c>
       <c r="C248">
-        <v>43591</v>
+        <v>43603</v>
       </c>
       <c r="D248">
-        <v>60969</v>
+        <v>61079</v>
       </c>
       <c r="E248">
-        <v>79047</v>
+        <v>79441</v>
       </c>
     </row>
     <row r="249" spans="1:5">
@@ -4587,13 +4587,13 @@
         <v>25742</v>
       </c>
       <c r="C249">
-        <v>34302</v>
+        <v>34305</v>
       </c>
       <c r="D249">
-        <v>51363</v>
+        <v>51421</v>
       </c>
       <c r="E249">
-        <v>70175</v>
+        <v>70488</v>
       </c>
     </row>
     <row r="250" spans="1:5">
@@ -4604,13 +4604,13 @@
         <v>49576</v>
       </c>
       <c r="C250">
-        <v>59671</v>
+        <v>59691</v>
       </c>
       <c r="D250">
-        <v>75543</v>
+        <v>75718</v>
       </c>
       <c r="E250">
-        <v>91493</v>
+        <v>91638</v>
       </c>
     </row>
     <row r="251" spans="1:5">
@@ -4621,13 +4621,13 @@
         <v>51005</v>
       </c>
       <c r="C251">
-        <v>61634</v>
+        <v>61700</v>
       </c>
       <c r="D251">
-        <v>77451</v>
+        <v>77645</v>
       </c>
       <c r="E251">
-        <v>92972</v>
+        <v>93103</v>
       </c>
     </row>
     <row r="252" spans="1:5">
@@ -4641,10 +4641,10 @@
         <v>56493</v>
       </c>
       <c r="D252">
-        <v>72229</v>
+        <v>72276</v>
       </c>
       <c r="E252">
-        <v>88496</v>
+        <v>88610</v>
       </c>
     </row>
     <row r="253" spans="1:5">
@@ -4655,13 +4655,13 @@
         <v>47518</v>
       </c>
       <c r="C253">
-        <v>57726</v>
+        <v>57768</v>
       </c>
       <c r="D253">
-        <v>74633</v>
+        <v>74753</v>
       </c>
       <c r="E253">
-        <v>91196</v>
+        <v>91309</v>
       </c>
     </row>
     <row r="254" spans="1:5">
@@ -4672,13 +4672,13 @@
         <v>50893</v>
       </c>
       <c r="C254">
-        <v>61177</v>
+        <v>61219</v>
       </c>
       <c r="D254">
-        <v>77635</v>
+        <v>77792</v>
       </c>
       <c r="E254">
-        <v>93797</v>
+        <v>93907</v>
       </c>
     </row>
     <row r="255" spans="1:5">
@@ -4689,13 +4689,13 @@
         <v>47518</v>
       </c>
       <c r="C255">
-        <v>57726</v>
+        <v>57768</v>
       </c>
       <c r="D255">
-        <v>74633</v>
+        <v>74753</v>
       </c>
       <c r="E255">
-        <v>91196</v>
+        <v>91309</v>
       </c>
     </row>
     <row r="256" spans="1:5">
@@ -4709,10 +4709,10 @@
         <v>55270</v>
       </c>
       <c r="D256">
-        <v>71046</v>
+        <v>71065</v>
       </c>
       <c r="E256">
-        <v>87455</v>
+        <v>87528</v>
       </c>
     </row>
     <row r="257" spans="1:5">
@@ -4726,10 +4726,10 @@
         <v>48400</v>
       </c>
       <c r="D257">
-        <v>64885</v>
+        <v>64902</v>
       </c>
       <c r="E257">
-        <v>82329</v>
+        <v>82423</v>
       </c>
     </row>
     <row r="258" spans="1:5">
@@ -4743,10 +4743,10 @@
         <v>48137</v>
       </c>
       <c r="D258">
-        <v>64587</v>
+        <v>64629</v>
       </c>
       <c r="E258">
-        <v>82418</v>
+        <v>82539</v>
       </c>
     </row>
     <row r="259" spans="1:5">
@@ -4760,10 +4760,10 @@
         <v>48137</v>
       </c>
       <c r="D259">
-        <v>64587</v>
+        <v>64629</v>
       </c>
       <c r="E259">
-        <v>82418</v>
+        <v>82539</v>
       </c>
     </row>
     <row r="260" spans="1:5">
@@ -4774,13 +4774,13 @@
         <v>15266</v>
       </c>
       <c r="C260">
-        <v>22887</v>
+        <v>22892</v>
       </c>
       <c r="D260">
-        <v>45717</v>
+        <v>45977</v>
       </c>
       <c r="E260">
-        <v>70866</v>
+        <v>71446</v>
       </c>
     </row>
     <row r="261" spans="1:5">
@@ -4794,10 +4794,10 @@
         <v>13876</v>
       </c>
       <c r="D261">
-        <v>34328</v>
+        <v>34379</v>
       </c>
       <c r="E261">
-        <v>58932</v>
+        <v>59211</v>
       </c>
     </row>
     <row r="262" spans="1:5">
@@ -4811,10 +4811,10 @@
         <v>21103</v>
       </c>
       <c r="D262">
-        <v>42645</v>
+        <v>42803</v>
       </c>
       <c r="E262">
-        <v>67386</v>
+        <v>67844</v>
       </c>
     </row>
     <row r="263" spans="1:5">
@@ -4825,13 +4825,13 @@
         <v>14850</v>
       </c>
       <c r="C263">
-        <v>21804</v>
+        <v>21805</v>
       </c>
       <c r="D263">
-        <v>43965</v>
+        <v>44118</v>
       </c>
       <c r="E263">
-        <v>69058</v>
+        <v>69497</v>
       </c>
     </row>
     <row r="264" spans="1:5">
@@ -4839,16 +4839,16 @@
         <v>263</v>
       </c>
       <c r="B264">
-        <v>13567</v>
+        <v>13568</v>
       </c>
       <c r="C264">
         <v>19513</v>
       </c>
       <c r="D264">
-        <v>40528</v>
+        <v>40578</v>
       </c>
       <c r="E264">
-        <v>65046</v>
+        <v>65329</v>
       </c>
     </row>
     <row r="265" spans="1:5">
@@ -4856,16 +4856,16 @@
         <v>264</v>
       </c>
       <c r="B265">
-        <v>13567</v>
+        <v>13568</v>
       </c>
       <c r="C265">
         <v>19513</v>
       </c>
       <c r="D265">
-        <v>40528</v>
+        <v>40578</v>
       </c>
       <c r="E265">
-        <v>65046</v>
+        <v>65329</v>
       </c>
     </row>
     <row r="266" spans="1:5">
@@ -4876,13 +4876,13 @@
         <v>18221</v>
       </c>
       <c r="C266">
-        <v>27063</v>
+        <v>27102</v>
       </c>
       <c r="D266">
-        <v>50450</v>
+        <v>50936</v>
       </c>
       <c r="E266">
-        <v>75671</v>
+        <v>76309</v>
       </c>
     </row>
     <row r="267" spans="1:5">
@@ -4890,16 +4890,16 @@
         <v>266</v>
       </c>
       <c r="B267">
-        <v>13567</v>
+        <v>13568</v>
       </c>
       <c r="C267">
         <v>19513</v>
       </c>
       <c r="D267">
-        <v>40528</v>
+        <v>40578</v>
       </c>
       <c r="E267">
-        <v>65046</v>
+        <v>65329</v>
       </c>
     </row>
     <row r="268" spans="1:5">
@@ -4913,10 +4913,10 @@
         <v>13876</v>
       </c>
       <c r="D268">
-        <v>34328</v>
+        <v>34379</v>
       </c>
       <c r="E268">
-        <v>58932</v>
+        <v>59211</v>
       </c>
     </row>
     <row r="269" spans="1:5">
@@ -4930,10 +4930,10 @@
         <v>13876</v>
       </c>
       <c r="D269">
-        <v>34328</v>
+        <v>34379</v>
       </c>
       <c r="E269">
-        <v>58932</v>
+        <v>59211</v>
       </c>
     </row>
     <row r="270" spans="1:5">
@@ -4944,13 +4944,13 @@
         <v>10034</v>
       </c>
       <c r="C270">
-        <v>17229</v>
+        <v>17235</v>
       </c>
       <c r="D270">
-        <v>39428</v>
+        <v>39558</v>
       </c>
       <c r="E270">
-        <v>63891</v>
+        <v>64324</v>
       </c>
     </row>
     <row r="271" spans="1:5">
@@ -4961,13 +4961,13 @@
         <v>7412</v>
       </c>
       <c r="C271">
-        <v>12812</v>
+        <v>12814</v>
       </c>
       <c r="D271">
-        <v>32041</v>
+        <v>32083</v>
       </c>
       <c r="E271">
-        <v>54338</v>
+        <v>54533</v>
       </c>
     </row>
     <row r="272" spans="1:5">
@@ -4978,13 +4978,13 @@
         <v>7412</v>
       </c>
       <c r="C272">
-        <v>12812</v>
+        <v>12814</v>
       </c>
       <c r="D272">
-        <v>32041</v>
+        <v>32083</v>
       </c>
       <c r="E272">
-        <v>54338</v>
+        <v>54533</v>
       </c>
     </row>
     <row r="273" spans="1:5">
@@ -4995,13 +4995,13 @@
         <v>11020</v>
       </c>
       <c r="C273">
-        <v>18825</v>
+        <v>18839</v>
       </c>
       <c r="D273">
-        <v>41988</v>
+        <v>42201</v>
       </c>
       <c r="E273">
-        <v>67107</v>
+        <v>67639</v>
       </c>
     </row>
     <row r="274" spans="1:5">
@@ -5012,13 +5012,13 @@
         <v>11020</v>
       </c>
       <c r="C274">
-        <v>18825</v>
+        <v>18839</v>
       </c>
       <c r="D274">
-        <v>41988</v>
+        <v>42201</v>
       </c>
       <c r="E274">
-        <v>67107</v>
+        <v>67639</v>
       </c>
     </row>
     <row r="275" spans="1:5">
@@ -5032,10 +5032,10 @@
         <v>20265</v>
       </c>
       <c r="D275">
-        <v>38745</v>
+        <v>38757</v>
       </c>
       <c r="E275">
-        <v>57672</v>
+        <v>57693</v>
       </c>
     </row>
     <row r="276" spans="1:5">
@@ -5049,10 +5049,10 @@
         <v>14078</v>
       </c>
       <c r="D276">
-        <v>31859</v>
+        <v>31876</v>
       </c>
       <c r="E276">
-        <v>49782</v>
+        <v>49824</v>
       </c>
     </row>
     <row r="277" spans="1:5">
@@ -5066,10 +5066,10 @@
         <v>26447</v>
       </c>
       <c r="D277">
-        <v>46470</v>
+        <v>46507</v>
       </c>
       <c r="E277">
-        <v>67023</v>
+        <v>67055</v>
       </c>
     </row>
     <row r="278" spans="1:5">
@@ -5080,13 +5080,13 @@
         <v>26274</v>
       </c>
       <c r="C278">
-        <v>36502</v>
+        <v>36508</v>
       </c>
       <c r="D278">
-        <v>56994</v>
+        <v>57051</v>
       </c>
       <c r="E278">
-        <v>77993</v>
+        <v>78045</v>
       </c>
     </row>
     <row r="279" spans="1:5">
@@ -5100,10 +5100,10 @@
         <v>39618</v>
       </c>
       <c r="D279">
-        <v>56595</v>
+        <v>56623</v>
       </c>
       <c r="E279">
-        <v>75059</v>
+        <v>75097</v>
       </c>
     </row>
     <row r="280" spans="1:5">
@@ -5117,10 +5117,10 @@
         <v>39618</v>
       </c>
       <c r="D280">
-        <v>56595</v>
+        <v>56623</v>
       </c>
       <c r="E280">
-        <v>75059</v>
+        <v>75097</v>
       </c>
     </row>
     <row r="281" spans="1:5">
@@ -5134,10 +5134,10 @@
         <v>15440</v>
       </c>
       <c r="D281">
-        <v>34376</v>
+        <v>34406</v>
       </c>
       <c r="E281">
-        <v>53385</v>
+        <v>53465</v>
       </c>
     </row>
     <row r="282" spans="1:5">
@@ -5148,13 +5148,13 @@
         <v>7996</v>
       </c>
       <c r="C282">
-        <v>13478</v>
+        <v>13481</v>
       </c>
       <c r="D282">
-        <v>31425</v>
+        <v>31442</v>
       </c>
       <c r="E282">
-        <v>49260</v>
+        <v>49311</v>
       </c>
     </row>
     <row r="283" spans="1:5">
@@ -5165,13 +5165,13 @@
         <v>7996</v>
       </c>
       <c r="C283">
-        <v>13478</v>
+        <v>13481</v>
       </c>
       <c r="D283">
-        <v>31425</v>
+        <v>31442</v>
       </c>
       <c r="E283">
-        <v>49260</v>
+        <v>49311</v>
       </c>
     </row>
     <row r="284" spans="1:5">
@@ -5182,13 +5182,13 @@
         <v>7996</v>
       </c>
       <c r="C284">
-        <v>13478</v>
+        <v>13481</v>
       </c>
       <c r="D284">
-        <v>31425</v>
+        <v>31442</v>
       </c>
       <c r="E284">
-        <v>49260</v>
+        <v>49311</v>
       </c>
     </row>
     <row r="285" spans="1:5">
@@ -5202,10 +5202,10 @@
         <v>14078</v>
       </c>
       <c r="D285">
-        <v>31859</v>
+        <v>31876</v>
       </c>
       <c r="E285">
-        <v>49782</v>
+        <v>49824</v>
       </c>
     </row>
     <row r="286" spans="1:5">
@@ -5219,10 +5219,10 @@
         <v>39618</v>
       </c>
       <c r="D286">
-        <v>56595</v>
+        <v>56623</v>
       </c>
       <c r="E286">
-        <v>75059</v>
+        <v>75097</v>
       </c>
     </row>
     <row r="287" spans="1:5">
@@ -5233,13 +5233,13 @@
         <v>36525</v>
       </c>
       <c r="C287">
-        <v>45225</v>
+        <v>45246</v>
       </c>
       <c r="D287">
-        <v>64428</v>
+        <v>64579</v>
       </c>
       <c r="E287">
-        <v>85590</v>
+        <v>85734</v>
       </c>
     </row>
     <row r="288" spans="1:5">
@@ -5250,13 +5250,13 @@
         <v>29780</v>
       </c>
       <c r="C288">
-        <v>39157</v>
+        <v>39182</v>
       </c>
       <c r="D288">
-        <v>59703</v>
+        <v>59901</v>
       </c>
       <c r="E288">
-        <v>81555</v>
+        <v>81761</v>
       </c>
     </row>
     <row r="289" spans="1:5">
@@ -5267,13 +5267,13 @@
         <v>38037</v>
       </c>
       <c r="C289">
-        <v>46467</v>
+        <v>46541</v>
       </c>
       <c r="D289">
-        <v>65438</v>
+        <v>65743</v>
       </c>
       <c r="E289">
-        <v>86246</v>
+        <v>86471</v>
       </c>
     </row>
     <row r="290" spans="1:5">
@@ -5284,13 +5284,13 @@
         <v>36525</v>
       </c>
       <c r="C290">
-        <v>45225</v>
+        <v>45246</v>
       </c>
       <c r="D290">
-        <v>64428</v>
+        <v>64579</v>
       </c>
       <c r="E290">
-        <v>85590</v>
+        <v>85734</v>
       </c>
     </row>
     <row r="291" spans="1:5">
@@ -5301,13 +5301,13 @@
         <v>27143</v>
       </c>
       <c r="C291">
-        <v>36134</v>
+        <v>36153</v>
       </c>
       <c r="D291">
-        <v>56856</v>
+        <v>56997</v>
       </c>
       <c r="E291">
-        <v>78796</v>
+        <v>78969</v>
       </c>
     </row>
     <row r="292" spans="1:5">
@@ -5318,13 +5318,13 @@
         <v>31714</v>
       </c>
       <c r="C292">
-        <v>40524</v>
+        <v>40525</v>
       </c>
       <c r="D292">
-        <v>59373</v>
+        <v>59472</v>
       </c>
       <c r="E292">
-        <v>79409</v>
+        <v>79571</v>
       </c>
     </row>
     <row r="293" spans="1:5">
@@ -5335,13 +5335,13 @@
         <v>32288</v>
       </c>
       <c r="C293">
-        <v>41337</v>
+        <v>41338</v>
       </c>
       <c r="D293">
-        <v>60556</v>
+        <v>60641</v>
       </c>
       <c r="E293">
-        <v>80834</v>
+        <v>80972</v>
       </c>
     </row>
     <row r="294" spans="1:5">
@@ -5352,13 +5352,13 @@
         <v>31714</v>
       </c>
       <c r="C294">
-        <v>40524</v>
+        <v>40525</v>
       </c>
       <c r="D294">
-        <v>59373</v>
+        <v>59472</v>
       </c>
       <c r="E294">
-        <v>79409</v>
+        <v>79571</v>
       </c>
     </row>
     <row r="295" spans="1:5">
@@ -5369,13 +5369,13 @@
         <v>27118</v>
       </c>
       <c r="C295">
-        <v>34232</v>
+        <v>34236</v>
       </c>
       <c r="D295">
-        <v>53929</v>
+        <v>53969</v>
       </c>
       <c r="E295">
-        <v>75695</v>
+        <v>75801</v>
       </c>
     </row>
     <row r="296" spans="1:5">
@@ -5386,13 +5386,13 @@
         <v>29337</v>
       </c>
       <c r="C296">
-        <v>37102</v>
+        <v>37109</v>
       </c>
       <c r="D296">
-        <v>57438</v>
+        <v>57506</v>
       </c>
       <c r="E296">
-        <v>79364</v>
+        <v>79500</v>
       </c>
     </row>
     <row r="297" spans="1:5">
@@ -5403,13 +5403,13 @@
         <v>28844</v>
       </c>
       <c r="C297">
-        <v>37896</v>
+        <v>37907</v>
       </c>
       <c r="D297">
-        <v>59763</v>
+        <v>59880</v>
       </c>
       <c r="E297">
-        <v>81985</v>
+        <v>82156</v>
       </c>
     </row>
     <row r="298" spans="1:5">
@@ -5420,13 +5420,13 @@
         <v>26007</v>
       </c>
       <c r="C298">
-        <v>33811</v>
+        <v>33818</v>
       </c>
       <c r="D298">
-        <v>54241</v>
+        <v>54288</v>
       </c>
       <c r="E298">
-        <v>76261</v>
+        <v>76388</v>
       </c>
     </row>
     <row r="299" spans="1:5">
@@ -5437,13 +5437,13 @@
         <v>25675</v>
       </c>
       <c r="C299">
-        <v>34141</v>
+        <v>34147</v>
       </c>
       <c r="D299">
-        <v>55715</v>
+        <v>55770</v>
       </c>
       <c r="E299">
-        <v>78226</v>
+        <v>78363</v>
       </c>
     </row>
     <row r="300" spans="1:5">
@@ -5454,13 +5454,13 @@
         <v>27118</v>
       </c>
       <c r="C300">
-        <v>34232</v>
+        <v>34236</v>
       </c>
       <c r="D300">
-        <v>53929</v>
+        <v>53969</v>
       </c>
       <c r="E300">
-        <v>75695</v>
+        <v>75801</v>
       </c>
     </row>
     <row r="301" spans="1:5">
@@ -5471,13 +5471,13 @@
         <v>29747</v>
       </c>
       <c r="C301">
-        <v>37961</v>
+        <v>37969</v>
       </c>
       <c r="D301">
-        <v>58805</v>
+        <v>58869</v>
       </c>
       <c r="E301">
-        <v>80862</v>
+        <v>80992</v>
       </c>
     </row>
     <row r="302" spans="1:5">
@@ -5488,13 +5488,13 @@
         <v>26817</v>
       </c>
       <c r="C302">
-        <v>35524</v>
+        <v>35529</v>
       </c>
       <c r="D302">
-        <v>56934</v>
+        <v>56975</v>
       </c>
       <c r="E302">
-        <v>79346</v>
+        <v>79461</v>
       </c>
     </row>
     <row r="303" spans="1:5">
@@ -5505,13 +5505,13 @@
         <v>26817</v>
       </c>
       <c r="C303">
-        <v>35524</v>
+        <v>35529</v>
       </c>
       <c r="D303">
-        <v>56934</v>
+        <v>56975</v>
       </c>
       <c r="E303">
-        <v>79346</v>
+        <v>79461</v>
       </c>
     </row>
     <row r="304" spans="1:5">
@@ -5522,13 +5522,13 @@
         <v>23972</v>
       </c>
       <c r="C304">
-        <v>31285</v>
+        <v>31289</v>
       </c>
       <c r="D304">
-        <v>51653</v>
+        <v>51725</v>
       </c>
       <c r="E304">
-        <v>73950</v>
+        <v>74155</v>
       </c>
     </row>
     <row r="305" spans="1:5">
@@ -5539,13 +5539,13 @@
         <v>23972</v>
       </c>
       <c r="C305">
-        <v>31285</v>
+        <v>31289</v>
       </c>
       <c r="D305">
-        <v>51653</v>
+        <v>51725</v>
       </c>
       <c r="E305">
-        <v>73950</v>
+        <v>74155</v>
       </c>
     </row>
     <row r="306" spans="1:5">
@@ -5556,13 +5556,13 @@
         <v>25396</v>
       </c>
       <c r="C306">
-        <v>30879</v>
+        <v>30883</v>
       </c>
       <c r="D306">
-        <v>49145</v>
+        <v>49171</v>
       </c>
       <c r="E306">
-        <v>70423</v>
+        <v>70559</v>
       </c>
     </row>
     <row r="307" spans="1:5">
@@ -5573,13 +5573,13 @@
         <v>23972</v>
       </c>
       <c r="C307">
-        <v>31285</v>
+        <v>31289</v>
       </c>
       <c r="D307">
-        <v>51653</v>
+        <v>51725</v>
       </c>
       <c r="E307">
-        <v>73950</v>
+        <v>74155</v>
       </c>
     </row>
     <row r="308" spans="1:5">
@@ -5590,13 +5590,13 @@
         <v>25661</v>
       </c>
       <c r="C308">
-        <v>31518</v>
+        <v>31520</v>
       </c>
       <c r="D308">
-        <v>50389</v>
+        <v>50413</v>
       </c>
       <c r="E308">
-        <v>72054</v>
+        <v>72187</v>
       </c>
     </row>
     <row r="309" spans="1:5">
@@ -5607,13 +5607,13 @@
         <v>25396</v>
       </c>
       <c r="C309">
-        <v>30879</v>
+        <v>30883</v>
       </c>
       <c r="D309">
-        <v>49145</v>
+        <v>49171</v>
       </c>
       <c r="E309">
-        <v>70423</v>
+        <v>70559</v>
       </c>
     </row>
     <row r="310" spans="1:5">
@@ -5624,13 +5624,13 @@
         <v>24325</v>
       </c>
       <c r="C310">
-        <v>32090</v>
+        <v>32093</v>
       </c>
       <c r="D310">
-        <v>53027</v>
+        <v>53097</v>
       </c>
       <c r="E310">
-        <v>75586</v>
+        <v>75785</v>
       </c>
     </row>
     <row r="311" spans="1:5">
@@ -5644,10 +5644,10 @@
         <v>15743</v>
       </c>
       <c r="D311">
-        <v>33490</v>
+        <v>33517</v>
       </c>
       <c r="E311">
-        <v>54468</v>
+        <v>54663</v>
       </c>
     </row>
     <row r="312" spans="1:5">
@@ -5661,10 +5661,10 @@
         <v>15743</v>
       </c>
       <c r="D312">
-        <v>33490</v>
+        <v>33517</v>
       </c>
       <c r="E312">
-        <v>54468</v>
+        <v>54663</v>
       </c>
     </row>
     <row r="313" spans="1:5">
@@ -5678,10 +5678,10 @@
         <v>15743</v>
       </c>
       <c r="D313">
-        <v>33490</v>
+        <v>33517</v>
       </c>
       <c r="E313">
-        <v>54468</v>
+        <v>54663</v>
       </c>
     </row>
     <row r="314" spans="1:5">
@@ -5695,10 +5695,10 @@
         <v>15743</v>
       </c>
       <c r="D314">
-        <v>33490</v>
+        <v>33517</v>
       </c>
       <c r="E314">
-        <v>54468</v>
+        <v>54663</v>
       </c>
     </row>
     <row r="315" spans="1:5">
@@ -5709,13 +5709,13 @@
         <v>39551</v>
       </c>
       <c r="C315">
-        <v>48428</v>
+        <v>48474</v>
       </c>
       <c r="D315">
-        <v>67376</v>
+        <v>67605</v>
       </c>
       <c r="E315">
-        <v>87390</v>
+        <v>87537</v>
       </c>
     </row>
     <row r="316" spans="1:5">
@@ -5726,13 +5726,13 @@
         <v>47248</v>
       </c>
       <c r="C316">
-        <v>55560</v>
+        <v>55577</v>
       </c>
       <c r="D316">
-        <v>72603</v>
+        <v>72703</v>
       </c>
       <c r="E316">
-        <v>91123</v>
+        <v>91195</v>
       </c>
     </row>
     <row r="317" spans="1:5">
@@ -5743,13 +5743,13 @@
         <v>46390</v>
       </c>
       <c r="C317">
-        <v>54206</v>
+        <v>54232</v>
       </c>
       <c r="D317">
-        <v>71094</v>
+        <v>71234</v>
       </c>
       <c r="E317">
-        <v>89842</v>
+        <v>89935</v>
       </c>
     </row>
     <row r="318" spans="1:5">
@@ -5760,13 +5760,13 @@
         <v>43480</v>
       </c>
       <c r="C318">
-        <v>51660</v>
+        <v>51701</v>
       </c>
       <c r="D318">
-        <v>69601</v>
+        <v>69802</v>
       </c>
       <c r="E318">
-        <v>89122</v>
+        <v>89246</v>
       </c>
     </row>
     <row r="319" spans="1:5">
@@ -5777,13 +5777,13 @@
         <v>38232</v>
       </c>
       <c r="C319">
-        <v>46333</v>
+        <v>46381</v>
       </c>
       <c r="D319">
-        <v>64728</v>
+        <v>64986</v>
       </c>
       <c r="E319">
-        <v>84869</v>
+        <v>85042</v>
       </c>
     </row>
     <row r="320" spans="1:5">
@@ -5794,13 +5794,13 @@
         <v>40674</v>
       </c>
       <c r="C320">
-        <v>48841</v>
+        <v>48883</v>
       </c>
       <c r="D320">
-        <v>66957</v>
+        <v>67188</v>
       </c>
       <c r="E320">
-        <v>86880</v>
+        <v>87040</v>
       </c>
     </row>
     <row r="321" spans="1:5">
@@ -5811,13 +5811,13 @@
         <v>43497</v>
       </c>
       <c r="C321">
-        <v>51518</v>
+        <v>51561</v>
       </c>
       <c r="D321">
-        <v>69106</v>
+        <v>69289</v>
       </c>
       <c r="E321">
-        <v>88518</v>
+        <v>88633</v>
       </c>
     </row>
     <row r="322" spans="1:5">
@@ -5828,13 +5828,13 @@
         <v>37581</v>
       </c>
       <c r="C322">
-        <v>46722</v>
+        <v>46757</v>
       </c>
       <c r="D322">
-        <v>66279</v>
+        <v>66471</v>
       </c>
       <c r="E322">
-        <v>86753</v>
+        <v>86899</v>
       </c>
     </row>
     <row r="323" spans="1:5">
@@ -5845,13 +5845,13 @@
         <v>40930</v>
       </c>
       <c r="C323">
-        <v>48565</v>
+        <v>48566</v>
       </c>
       <c r="D323">
-        <v>66304</v>
+        <v>66434</v>
       </c>
       <c r="E323">
-        <v>86215</v>
+        <v>86316</v>
       </c>
     </row>
     <row r="324" spans="1:5">
@@ -5862,13 +5862,13 @@
         <v>40930</v>
       </c>
       <c r="C324">
-        <v>48565</v>
+        <v>48566</v>
       </c>
       <c r="D324">
-        <v>66304</v>
+        <v>66434</v>
       </c>
       <c r="E324">
-        <v>86215</v>
+        <v>86316</v>
       </c>
     </row>
     <row r="325" spans="1:5">
@@ -5879,13 +5879,13 @@
         <v>40930</v>
       </c>
       <c r="C325">
-        <v>48565</v>
+        <v>48566</v>
       </c>
       <c r="D325">
-        <v>66304</v>
+        <v>66434</v>
       </c>
       <c r="E325">
-        <v>86215</v>
+        <v>86316</v>
       </c>
     </row>
     <row r="326" spans="1:5">
@@ -5896,13 +5896,13 @@
         <v>46027</v>
       </c>
       <c r="C326">
-        <v>54048</v>
+        <v>54055</v>
       </c>
       <c r="D326">
-        <v>70903</v>
+        <v>71010</v>
       </c>
       <c r="E326">
-        <v>89675</v>
+        <v>89747</v>
       </c>
     </row>
     <row r="327" spans="1:5">
@@ -5913,13 +5913,13 @@
         <v>34728</v>
       </c>
       <c r="C327">
-        <v>43954</v>
+        <v>43972</v>
       </c>
       <c r="D327">
-        <v>63684</v>
+        <v>63991</v>
       </c>
       <c r="E327">
-        <v>84312</v>
+        <v>84553</v>
       </c>
     </row>
     <row r="328" spans="1:5">
@@ -5930,13 +5930,13 @@
         <v>34728</v>
       </c>
       <c r="C328">
-        <v>43954</v>
+        <v>43972</v>
       </c>
       <c r="D328">
-        <v>63684</v>
+        <v>63991</v>
       </c>
       <c r="E328">
-        <v>84312</v>
+        <v>84553</v>
       </c>
     </row>
     <row r="329" spans="1:5">
@@ -5947,13 +5947,13 @@
         <v>32531</v>
       </c>
       <c r="C329">
-        <v>41468</v>
+        <v>41476</v>
       </c>
       <c r="D329">
-        <v>61613</v>
+        <v>61809</v>
       </c>
       <c r="E329">
-        <v>82766</v>
+        <v>82953</v>
       </c>
     </row>
     <row r="330" spans="1:5">
@@ -5964,13 +5964,13 @@
         <v>34728</v>
       </c>
       <c r="C330">
-        <v>43954</v>
+        <v>43972</v>
       </c>
       <c r="D330">
-        <v>63684</v>
+        <v>63991</v>
       </c>
       <c r="E330">
-        <v>84312</v>
+        <v>84553</v>
       </c>
     </row>
     <row r="331" spans="1:5">
@@ -5981,13 +5981,13 @@
         <v>34212</v>
       </c>
       <c r="C331">
-        <v>42980</v>
+        <v>42999</v>
       </c>
       <c r="D331">
-        <v>62415</v>
+        <v>62732</v>
       </c>
       <c r="E331">
-        <v>83024</v>
+        <v>83281</v>
       </c>
     </row>
     <row r="332" spans="1:5">
@@ -5998,13 +5998,13 @@
         <v>39270</v>
       </c>
       <c r="C332">
-        <v>48104</v>
+        <v>48116</v>
       </c>
       <c r="D332">
-        <v>68155</v>
+        <v>68376</v>
       </c>
       <c r="E332">
-        <v>88559</v>
+        <v>88727</v>
       </c>
     </row>
     <row r="333" spans="1:5">
@@ -6015,13 +6015,13 @@
         <v>41705</v>
       </c>
       <c r="C333">
-        <v>51014</v>
+        <v>51025</v>
       </c>
       <c r="D333">
-        <v>71200</v>
+        <v>71347</v>
       </c>
       <c r="E333">
-        <v>90788</v>
+        <v>90899</v>
       </c>
     </row>
     <row r="334" spans="1:5">
@@ -6032,13 +6032,13 @@
         <v>45079</v>
       </c>
       <c r="C334">
-        <v>55230</v>
+        <v>55248</v>
       </c>
       <c r="D334">
-        <v>75209</v>
+        <v>75387</v>
       </c>
       <c r="E334">
-        <v>93721</v>
+        <v>93837</v>
       </c>
     </row>
     <row r="335" spans="1:5">
@@ -6049,13 +6049,13 @@
         <v>41881</v>
       </c>
       <c r="C335">
-        <v>52221</v>
+        <v>52242</v>
       </c>
       <c r="D335">
-        <v>73038</v>
+        <v>73219</v>
       </c>
       <c r="E335">
-        <v>92266</v>
+        <v>92382</v>
       </c>
     </row>
     <row r="336" spans="1:5">
@@ -6066,13 +6066,13 @@
         <v>36755</v>
       </c>
       <c r="C336">
-        <v>45075</v>
+        <v>45081</v>
       </c>
       <c r="D336">
-        <v>65051</v>
+        <v>65275</v>
       </c>
       <c r="E336">
-        <v>85887</v>
+        <v>86076</v>
       </c>
     </row>
     <row r="337" spans="1:5">
@@ -6086,10 +6086,10 @@
         <v>24601</v>
       </c>
       <c r="D337">
-        <v>37953</v>
+        <v>37986</v>
       </c>
       <c r="E337">
-        <v>50640</v>
+        <v>50653</v>
       </c>
     </row>
     <row r="338" spans="1:5">
@@ -6103,10 +6103,10 @@
         <v>24979</v>
       </c>
       <c r="D338">
-        <v>39041</v>
+        <v>39051</v>
       </c>
       <c r="E338">
-        <v>51830</v>
+        <v>51837</v>
       </c>
     </row>
     <row r="339" spans="1:5">
@@ -6120,10 +6120,10 @@
         <v>24601</v>
       </c>
       <c r="D339">
-        <v>37953</v>
+        <v>37986</v>
       </c>
       <c r="E339">
-        <v>50640</v>
+        <v>50653</v>
       </c>
     </row>
     <row r="340" spans="1:5">
@@ -6137,10 +6137,10 @@
         <v>21696</v>
       </c>
       <c r="D340">
-        <v>35269</v>
+        <v>35278</v>
       </c>
       <c r="E340">
-        <v>47670</v>
+        <v>47679</v>
       </c>
     </row>
     <row r="341" spans="1:5">
@@ -6154,10 +6154,10 @@
         <v>21696</v>
       </c>
       <c r="D341">
-        <v>35269</v>
+        <v>35278</v>
       </c>
       <c r="E341">
-        <v>47670</v>
+        <v>47679</v>
       </c>
     </row>
     <row r="342" spans="1:5">
@@ -6168,13 +6168,13 @@
         <v>17384</v>
       </c>
       <c r="C342">
-        <v>25107</v>
+        <v>25114</v>
       </c>
       <c r="D342">
-        <v>39754</v>
+        <v>39772</v>
       </c>
       <c r="E342">
-        <v>53503</v>
+        <v>53515</v>
       </c>
     </row>
     <row r="343" spans="1:5">
@@ -6185,13 +6185,13 @@
         <v>17384</v>
       </c>
       <c r="C343">
-        <v>25107</v>
+        <v>25114</v>
       </c>
       <c r="D343">
-        <v>39754</v>
+        <v>39772</v>
       </c>
       <c r="E343">
-        <v>53503</v>
+        <v>53515</v>
       </c>
     </row>
     <row r="344" spans="1:5">
@@ -6205,10 +6205,10 @@
         <v>21696</v>
       </c>
       <c r="D344">
-        <v>35269</v>
+        <v>35278</v>
       </c>
       <c r="E344">
-        <v>47670</v>
+        <v>47679</v>
       </c>
     </row>
     <row r="345" spans="1:5">
@@ -6222,10 +6222,10 @@
         <v>16101</v>
       </c>
       <c r="D345">
-        <v>29536</v>
+        <v>29540</v>
       </c>
       <c r="E345">
-        <v>41602</v>
+        <v>41611</v>
       </c>
     </row>
     <row r="346" spans="1:5">
@@ -6239,10 +6239,10 @@
         <v>16101</v>
       </c>
       <c r="D346">
-        <v>29536</v>
+        <v>29540</v>
       </c>
       <c r="E346">
-        <v>41602</v>
+        <v>41611</v>
       </c>
     </row>
     <row r="347" spans="1:5">
@@ -6256,10 +6256,10 @@
         <v>16101</v>
       </c>
       <c r="D347">
-        <v>29536</v>
+        <v>29540</v>
       </c>
       <c r="E347">
-        <v>41602</v>
+        <v>41611</v>
       </c>
     </row>
     <row r="348" spans="1:5">
@@ -6273,10 +6273,10 @@
         <v>25498</v>
       </c>
       <c r="D348">
-        <v>38122</v>
+        <v>38137</v>
       </c>
       <c r="E348">
-        <v>50156</v>
+        <v>50167</v>
       </c>
     </row>
     <row r="349" spans="1:5">
@@ -6290,10 +6290,10 @@
         <v>25498</v>
       </c>
       <c r="D349">
-        <v>38122</v>
+        <v>38137</v>
       </c>
       <c r="E349">
-        <v>50156</v>
+        <v>50167</v>
       </c>
     </row>
     <row r="350" spans="1:5">
@@ -6307,10 +6307,10 @@
         <v>25498</v>
       </c>
       <c r="D350">
-        <v>38122</v>
+        <v>38137</v>
       </c>
       <c r="E350">
-        <v>50156</v>
+        <v>50167</v>
       </c>
     </row>
     <row r="351" spans="1:5">
@@ -6321,13 +6321,13 @@
         <v>8205</v>
       </c>
       <c r="C351">
-        <v>13740</v>
+        <v>13741</v>
       </c>
       <c r="D351">
-        <v>27164</v>
+        <v>27174</v>
       </c>
       <c r="E351">
-        <v>38146</v>
+        <v>38161</v>
       </c>
     </row>
     <row r="352" spans="1:5">
@@ -6338,13 +6338,13 @@
         <v>8205</v>
       </c>
       <c r="C352">
-        <v>13740</v>
+        <v>13741</v>
       </c>
       <c r="D352">
-        <v>27164</v>
+        <v>27174</v>
       </c>
       <c r="E352">
-        <v>38146</v>
+        <v>38161</v>
       </c>
     </row>
     <row r="353" spans="1:5">
@@ -6355,13 +6355,13 @@
         <v>23929</v>
       </c>
       <c r="C353">
-        <v>30889</v>
+        <v>30892</v>
       </c>
       <c r="D353">
-        <v>44546</v>
+        <v>44571</v>
       </c>
       <c r="E353">
-        <v>60024</v>
+        <v>60160</v>
       </c>
     </row>
     <row r="354" spans="1:5">
@@ -6375,10 +6375,10 @@
         <v>27646</v>
       </c>
       <c r="D354">
-        <v>39089</v>
+        <v>39093</v>
       </c>
       <c r="E354">
-        <v>51824</v>
+        <v>51862</v>
       </c>
     </row>
     <row r="355" spans="1:5">
@@ -6389,13 +6389,13 @@
         <v>23929</v>
       </c>
       <c r="C355">
-        <v>30889</v>
+        <v>30892</v>
       </c>
       <c r="D355">
-        <v>44546</v>
+        <v>44571</v>
       </c>
       <c r="E355">
-        <v>60024</v>
+        <v>60160</v>
       </c>
     </row>
     <row r="356" spans="1:5">
@@ -6409,10 +6409,10 @@
         <v>24177</v>
       </c>
       <c r="D356">
-        <v>36376</v>
+        <v>36378</v>
       </c>
       <c r="E356">
-        <v>48459</v>
+        <v>48483</v>
       </c>
     </row>
     <row r="357" spans="1:5">
@@ -6426,10 +6426,10 @@
         <v>24177</v>
       </c>
       <c r="D357">
-        <v>36376</v>
+        <v>36378</v>
       </c>
       <c r="E357">
-        <v>48459</v>
+        <v>48483</v>
       </c>
     </row>
     <row r="358" spans="1:5">
@@ -6443,10 +6443,10 @@
         <v>24177</v>
       </c>
       <c r="D358">
-        <v>36376</v>
+        <v>36378</v>
       </c>
       <c r="E358">
-        <v>48459</v>
+        <v>48483</v>
       </c>
     </row>
     <row r="359" spans="1:5">
@@ -6457,13 +6457,13 @@
         <v>9227</v>
       </c>
       <c r="C359">
-        <v>14984</v>
+        <v>14985</v>
       </c>
       <c r="D359">
-        <v>28418</v>
+        <v>28425</v>
       </c>
       <c r="E359">
-        <v>39362</v>
+        <v>39371</v>
       </c>
     </row>
     <row r="360" spans="1:5">
@@ -6474,13 +6474,13 @@
         <v>9227</v>
       </c>
       <c r="C360">
-        <v>14984</v>
+        <v>14985</v>
       </c>
       <c r="D360">
-        <v>28418</v>
+        <v>28425</v>
       </c>
       <c r="E360">
-        <v>39362</v>
+        <v>39371</v>
       </c>
     </row>
     <row r="361" spans="1:5">
@@ -6494,10 +6494,10 @@
         <v>38162</v>
       </c>
       <c r="D361">
-        <v>60290</v>
+        <v>60339</v>
       </c>
       <c r="E361">
-        <v>82015</v>
+        <v>82101</v>
       </c>
     </row>
     <row r="362" spans="1:5">
@@ -6508,13 +6508,13 @@
         <v>19817</v>
       </c>
       <c r="C362">
-        <v>29276</v>
+        <v>29279</v>
       </c>
       <c r="D362">
-        <v>53928</v>
+        <v>54174</v>
       </c>
       <c r="E362">
-        <v>78058</v>
+        <v>78530</v>
       </c>
     </row>
     <row r="363" spans="1:5">
@@ -6528,10 +6528,10 @@
         <v>27927</v>
       </c>
       <c r="D363">
-        <v>50453</v>
+        <v>50511</v>
       </c>
       <c r="E363">
-        <v>74571</v>
+        <v>74858</v>
       </c>
     </row>
     <row r="364" spans="1:5">
@@ -6545,10 +6545,10 @@
         <v>34778</v>
       </c>
       <c r="D364">
-        <v>57337</v>
+        <v>57356</v>
       </c>
       <c r="E364">
-        <v>80855</v>
+        <v>80927</v>
       </c>
     </row>
     <row r="365" spans="1:5">
@@ -6562,10 +6562,10 @@
         <v>34778</v>
       </c>
       <c r="D365">
-        <v>57337</v>
+        <v>57356</v>
       </c>
       <c r="E365">
-        <v>80855</v>
+        <v>80927</v>
       </c>
     </row>
     <row r="366" spans="1:5">
@@ -6579,10 +6579,10 @@
         <v>26487</v>
       </c>
       <c r="D366">
-        <v>49387</v>
+        <v>49409</v>
       </c>
       <c r="E366">
-        <v>74030</v>
+        <v>74111</v>
       </c>
     </row>
     <row r="367" spans="1:5">
@@ -6596,10 +6596,10 @@
         <v>26487</v>
       </c>
       <c r="D367">
-        <v>49387</v>
+        <v>49409</v>
       </c>
       <c r="E367">
-        <v>74030</v>
+        <v>74111</v>
       </c>
     </row>
     <row r="368" spans="1:5">
@@ -6613,10 +6613,10 @@
         <v>28885</v>
       </c>
       <c r="D368">
-        <v>51231</v>
+        <v>51243</v>
       </c>
       <c r="E368">
-        <v>75377</v>
+        <v>75445</v>
       </c>
     </row>
     <row r="369" spans="1:5">
@@ -6630,10 +6630,10 @@
         <v>26487</v>
       </c>
       <c r="D369">
-        <v>49387</v>
+        <v>49409</v>
       </c>
       <c r="E369">
-        <v>74030</v>
+        <v>74111</v>
       </c>
     </row>
     <row r="370" spans="1:5">
@@ -6644,13 +6644,13 @@
         <v>12604</v>
       </c>
       <c r="C370">
-        <v>19507</v>
+        <v>19508</v>
       </c>
       <c r="D370">
-        <v>42151</v>
+        <v>42237</v>
       </c>
       <c r="E370">
-        <v>66871</v>
+        <v>67242</v>
       </c>
     </row>
     <row r="371" spans="1:5">
@@ -6661,13 +6661,13 @@
         <v>12604</v>
       </c>
       <c r="C371">
-        <v>19507</v>
+        <v>19508</v>
       </c>
       <c r="D371">
-        <v>42151</v>
+        <v>42237</v>
       </c>
       <c r="E371">
-        <v>66871</v>
+        <v>67242</v>
       </c>
     </row>
     <row r="372" spans="1:5">
@@ -6678,13 +6678,13 @@
         <v>12604</v>
       </c>
       <c r="C372">
-        <v>19507</v>
+        <v>19508</v>
       </c>
       <c r="D372">
-        <v>42151</v>
+        <v>42237</v>
       </c>
       <c r="E372">
-        <v>66871</v>
+        <v>67242</v>
       </c>
     </row>
     <row r="373" spans="1:5">
@@ -6698,10 +6698,10 @@
         <v>37163</v>
       </c>
       <c r="D373">
-        <v>53387</v>
+        <v>53412</v>
       </c>
       <c r="E373">
-        <v>69544</v>
+        <v>69557</v>
       </c>
     </row>
     <row r="374" spans="1:5">
@@ -6715,10 +6715,10 @@
         <v>30659</v>
       </c>
       <c r="D374">
-        <v>46061</v>
+        <v>46101</v>
       </c>
       <c r="E374">
-        <v>61963</v>
+        <v>61976</v>
       </c>
     </row>
     <row r="375" spans="1:5">
@@ -6732,10 +6732,10 @@
         <v>37163</v>
       </c>
       <c r="D375">
-        <v>53387</v>
+        <v>53412</v>
       </c>
       <c r="E375">
-        <v>69544</v>
+        <v>69557</v>
       </c>
     </row>
     <row r="376" spans="1:5">
@@ -6749,10 +6749,10 @@
         <v>30610</v>
       </c>
       <c r="D376">
-        <v>46385</v>
+        <v>46421</v>
       </c>
       <c r="E376">
-        <v>62638</v>
+        <v>62650</v>
       </c>
     </row>
     <row r="377" spans="1:5">
@@ -6766,10 +6766,10 @@
         <v>30610</v>
       </c>
       <c r="D377">
-        <v>46385</v>
+        <v>46421</v>
       </c>
       <c r="E377">
-        <v>62638</v>
+        <v>62650</v>
       </c>
     </row>
     <row r="378" spans="1:5">
@@ -6783,10 +6783,10 @@
         <v>43236</v>
       </c>
       <c r="D378">
-        <v>58126</v>
+        <v>58133</v>
       </c>
       <c r="E378">
-        <v>74113</v>
+        <v>74150</v>
       </c>
     </row>
     <row r="379" spans="1:5">
@@ -6800,10 +6800,10 @@
         <v>43236</v>
       </c>
       <c r="D379">
-        <v>58126</v>
+        <v>58133</v>
       </c>
       <c r="E379">
-        <v>74113</v>
+        <v>74150</v>
       </c>
     </row>
     <row r="380" spans="1:5">
@@ -6817,10 +6817,10 @@
         <v>43236</v>
       </c>
       <c r="D380">
-        <v>58126</v>
+        <v>58133</v>
       </c>
       <c r="E380">
-        <v>74113</v>
+        <v>74150</v>
       </c>
     </row>
     <row r="381" spans="1:5">
@@ -6834,10 +6834,10 @@
         <v>43236</v>
       </c>
       <c r="D381">
-        <v>58126</v>
+        <v>58133</v>
       </c>
       <c r="E381">
-        <v>74113</v>
+        <v>74150</v>
       </c>
     </row>
     <row r="382" spans="1:5">
@@ -6848,13 +6848,13 @@
         <v>30897</v>
       </c>
       <c r="C382">
-        <v>39208</v>
+        <v>39210</v>
       </c>
       <c r="D382">
-        <v>53867</v>
+        <v>53881</v>
       </c>
       <c r="E382">
-        <v>69810</v>
+        <v>69842</v>
       </c>
     </row>
     <row r="383" spans="1:5">
@@ -6868,10 +6868,10 @@
         <v>38982</v>
       </c>
       <c r="D383">
-        <v>56347</v>
+        <v>56364</v>
       </c>
       <c r="E383">
-        <v>74448</v>
+        <v>74523</v>
       </c>
     </row>
     <row r="384" spans="1:5">
@@ -6885,10 +6885,10 @@
         <v>36308</v>
       </c>
       <c r="D384">
-        <v>53624</v>
+        <v>53632</v>
       </c>
       <c r="E384">
-        <v>71445</v>
+        <v>71467</v>
       </c>
     </row>
     <row r="385" spans="1:5">
@@ -6902,10 +6902,10 @@
         <v>49149</v>
       </c>
       <c r="D385">
-        <v>65508</v>
+        <v>65544</v>
       </c>
       <c r="E385">
-        <v>82593</v>
+        <v>82663</v>
       </c>
     </row>
     <row r="386" spans="1:5">
@@ -6919,10 +6919,10 @@
         <v>28061</v>
       </c>
       <c r="D386">
-        <v>46479</v>
+        <v>46514</v>
       </c>
       <c r="E386">
-        <v>65896</v>
+        <v>66066</v>
       </c>
     </row>
     <row r="387" spans="1:5">
@@ -6936,10 +6936,10 @@
         <v>28061</v>
       </c>
       <c r="D387">
-        <v>46479</v>
+        <v>46514</v>
       </c>
       <c r="E387">
-        <v>65896</v>
+        <v>66066</v>
       </c>
     </row>
     <row r="388" spans="1:5">
@@ -6956,7 +6956,7 @@
         <v>24731</v>
       </c>
       <c r="E388">
-        <v>42447</v>
+        <v>42449</v>
       </c>
     </row>
     <row r="389" spans="1:5">
@@ -6970,10 +6970,10 @@
         <v>9111</v>
       </c>
       <c r="D389">
-        <v>25282</v>
+        <v>25283</v>
       </c>
       <c r="E389">
-        <v>45359</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="390" spans="1:5">
@@ -6987,10 +6987,10 @@
         <v>9111</v>
       </c>
       <c r="D390">
-        <v>25282</v>
+        <v>25283</v>
       </c>
       <c r="E390">
-        <v>45359</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="391" spans="1:5">
@@ -7007,7 +7007,7 @@
         <v>24731</v>
       </c>
       <c r="E391">
-        <v>42447</v>
+        <v>42449</v>
       </c>
     </row>
     <row r="392" spans="1:5">
@@ -7021,10 +7021,10 @@
         <v>9111</v>
       </c>
       <c r="D392">
-        <v>25282</v>
+        <v>25283</v>
       </c>
       <c r="E392">
-        <v>45359</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="393" spans="1:5">
@@ -7038,10 +7038,10 @@
         <v>7475</v>
       </c>
       <c r="D393">
-        <v>19176</v>
+        <v>19178</v>
       </c>
       <c r="E393">
-        <v>32920</v>
+        <v>32928</v>
       </c>
     </row>
     <row r="394" spans="1:5">
@@ -7055,10 +7055,10 @@
         <v>7475</v>
       </c>
       <c r="D394">
-        <v>19176</v>
+        <v>19178</v>
       </c>
       <c r="E394">
-        <v>32920</v>
+        <v>32928</v>
       </c>
     </row>
     <row r="395" spans="1:5">
@@ -7072,10 +7072,10 @@
         <v>8268</v>
       </c>
       <c r="D395">
-        <v>20433</v>
+        <v>20435</v>
       </c>
       <c r="E395">
-        <v>34784</v>
+        <v>34798</v>
       </c>
     </row>
     <row r="396" spans="1:5">
@@ -7089,10 +7089,10 @@
         <v>8268</v>
       </c>
       <c r="D396">
-        <v>20433</v>
+        <v>20435</v>
       </c>
       <c r="E396">
-        <v>34784</v>
+        <v>34798</v>
       </c>
     </row>
     <row r="397" spans="1:5">
@@ -7106,10 +7106,10 @@
         <v>9119</v>
       </c>
       <c r="D397">
-        <v>21641</v>
+        <v>21643</v>
       </c>
       <c r="E397">
-        <v>36971</v>
+        <v>36996</v>
       </c>
     </row>
     <row r="398" spans="1:5">
@@ -7123,10 +7123,10 @@
         <v>9119</v>
       </c>
       <c r="D398">
-        <v>21641</v>
+        <v>21643</v>
       </c>
       <c r="E398">
-        <v>36971</v>
+        <v>36996</v>
       </c>
     </row>
     <row r="399" spans="1:5">
@@ -7140,10 +7140,10 @@
         <v>8807</v>
       </c>
       <c r="D399">
-        <v>26557</v>
+        <v>26558</v>
       </c>
       <c r="E399">
-        <v>48538</v>
+        <v>48563</v>
       </c>
     </row>
     <row r="400" spans="1:5">
@@ -7157,10 +7157,10 @@
         <v>8267</v>
       </c>
       <c r="D400">
-        <v>26048</v>
+        <v>26050</v>
       </c>
       <c r="E400">
-        <v>48231</v>
+        <v>48273</v>
       </c>
     </row>
     <row r="401" spans="1:5">
@@ -7174,10 +7174,10 @@
         <v>8807</v>
       </c>
       <c r="D401">
-        <v>26557</v>
+        <v>26558</v>
       </c>
       <c r="E401">
-        <v>48538</v>
+        <v>48563</v>
       </c>
     </row>
     <row r="402" spans="1:5">
@@ -7191,10 +7191,10 @@
         <v>7740</v>
       </c>
       <c r="D402">
-        <v>23954</v>
+        <v>23955</v>
       </c>
       <c r="E402">
-        <v>44288</v>
+        <v>44343</v>
       </c>
     </row>
     <row r="403" spans="1:5">
@@ -7208,10 +7208,10 @@
         <v>8267</v>
       </c>
       <c r="D403">
-        <v>26048</v>
+        <v>26050</v>
       </c>
       <c r="E403">
-        <v>48231</v>
+        <v>48273</v>
       </c>
     </row>
     <row r="404" spans="1:5">
@@ -7225,10 +7225,10 @@
         <v>6996</v>
       </c>
       <c r="D404">
-        <v>23276</v>
+        <v>23277</v>
       </c>
       <c r="E404">
-        <v>43544</v>
+        <v>43570</v>
       </c>
     </row>
     <row r="405" spans="1:5">
@@ -7242,10 +7242,10 @@
         <v>6996</v>
       </c>
       <c r="D405">
-        <v>23276</v>
+        <v>23277</v>
       </c>
       <c r="E405">
-        <v>43544</v>
+        <v>43570</v>
       </c>
     </row>
     <row r="406" spans="1:5">
@@ -7259,10 +7259,10 @@
         <v>6996</v>
       </c>
       <c r="D406">
-        <v>23276</v>
+        <v>23277</v>
       </c>
       <c r="E406">
-        <v>43544</v>
+        <v>43570</v>
       </c>
     </row>
     <row r="407" spans="1:5">
@@ -7279,7 +7279,7 @@
         <v>21520</v>
       </c>
       <c r="E407">
-        <v>40652</v>
+        <v>40668</v>
       </c>
     </row>
     <row r="408" spans="1:5">
@@ -7296,7 +7296,7 @@
         <v>21520</v>
       </c>
       <c r="E408">
-        <v>40652</v>
+        <v>40668</v>
       </c>
     </row>
     <row r="409" spans="1:5">
@@ -7313,7 +7313,7 @@
         <v>21520</v>
       </c>
       <c r="E409">
-        <v>40652</v>
+        <v>40668</v>
       </c>
     </row>
     <row r="410" spans="1:5">
@@ -7327,10 +7327,10 @@
         <v>19345</v>
       </c>
       <c r="D410">
-        <v>43293</v>
+        <v>43320</v>
       </c>
       <c r="E410">
-        <v>69590</v>
+        <v>69745</v>
       </c>
     </row>
     <row r="411" spans="1:5">
@@ -7344,10 +7344,10 @@
         <v>15096</v>
       </c>
       <c r="D411">
-        <v>36832</v>
+        <v>36840</v>
       </c>
       <c r="E411">
-        <v>62221</v>
+        <v>62347</v>
       </c>
     </row>
     <row r="412" spans="1:5">
@@ -7361,10 +7361,10 @@
         <v>15096</v>
       </c>
       <c r="D412">
-        <v>36832</v>
+        <v>36840</v>
       </c>
       <c r="E412">
-        <v>62221</v>
+        <v>62347</v>
       </c>
     </row>
     <row r="413" spans="1:5">
@@ -7375,13 +7375,13 @@
         <v>8044</v>
       </c>
       <c r="C413">
-        <v>14096</v>
+        <v>14099</v>
       </c>
       <c r="D413">
-        <v>35720</v>
+        <v>35805</v>
       </c>
       <c r="E413">
-        <v>60499</v>
+        <v>60836</v>
       </c>
     </row>
     <row r="414" spans="1:5">
@@ -7395,10 +7395,10 @@
         <v>19345</v>
       </c>
       <c r="D414">
-        <v>43293</v>
+        <v>43320</v>
       </c>
       <c r="E414">
-        <v>69590</v>
+        <v>69745</v>
       </c>
     </row>
     <row r="415" spans="1:5">
@@ -7412,10 +7412,10 @@
         <v>17254</v>
       </c>
       <c r="D415">
-        <v>40236</v>
+        <v>40249</v>
       </c>
       <c r="E415">
-        <v>66439</v>
+        <v>66491</v>
       </c>
     </row>
     <row r="416" spans="1:5">
@@ -7429,10 +7429,10 @@
         <v>17254</v>
       </c>
       <c r="D416">
-        <v>40236</v>
+        <v>40249</v>
       </c>
       <c r="E416">
-        <v>66439</v>
+        <v>66491</v>
       </c>
     </row>
     <row r="417" spans="1:5">
@@ -7446,10 +7446,10 @@
         <v>11037</v>
       </c>
       <c r="D417">
-        <v>30842</v>
+        <v>30870</v>
       </c>
       <c r="E417">
-        <v>55123</v>
+        <v>55317</v>
       </c>
     </row>
     <row r="418" spans="1:5">
@@ -7463,10 +7463,10 @@
         <v>11037</v>
       </c>
       <c r="D418">
-        <v>30842</v>
+        <v>30870</v>
       </c>
       <c r="E418">
-        <v>55123</v>
+        <v>55317</v>
       </c>
     </row>
     <row r="419" spans="1:5">
@@ -7480,10 +7480,10 @@
         <v>17864</v>
       </c>
       <c r="D419">
-        <v>36187</v>
+        <v>36191</v>
       </c>
       <c r="E419">
-        <v>58231</v>
+        <v>58280</v>
       </c>
     </row>
     <row r="420" spans="1:5">
@@ -7497,10 +7497,10 @@
         <v>17864</v>
       </c>
       <c r="D420">
-        <v>36187</v>
+        <v>36191</v>
       </c>
       <c r="E420">
-        <v>58231</v>
+        <v>58280</v>
       </c>
     </row>
     <row r="421" spans="1:5">
@@ -7514,10 +7514,10 @@
         <v>17431</v>
       </c>
       <c r="D421">
-        <v>35156</v>
+        <v>35161</v>
       </c>
       <c r="E421">
-        <v>56563</v>
+        <v>56614</v>
       </c>
     </row>
     <row r="422" spans="1:5">
@@ -7531,10 +7531,10 @@
         <v>17431</v>
       </c>
       <c r="D422">
-        <v>35156</v>
+        <v>35161</v>
       </c>
       <c r="E422">
-        <v>56563</v>
+        <v>56614</v>
       </c>
     </row>
     <row r="423" spans="1:5">
@@ -7548,10 +7548,10 @@
         <v>17864</v>
       </c>
       <c r="D423">
-        <v>36187</v>
+        <v>36191</v>
       </c>
       <c r="E423">
-        <v>58231</v>
+        <v>58280</v>
       </c>
     </row>
     <row r="424" spans="1:5">
@@ -7565,10 +7565,10 @@
         <v>17864</v>
       </c>
       <c r="D424">
-        <v>36187</v>
+        <v>36191</v>
       </c>
       <c r="E424">
-        <v>58231</v>
+        <v>58280</v>
       </c>
     </row>
     <row r="425" spans="1:5">
@@ -7582,10 +7582,10 @@
         <v>17431</v>
       </c>
       <c r="D425">
-        <v>35156</v>
+        <v>35161</v>
       </c>
       <c r="E425">
-        <v>56563</v>
+        <v>56614</v>
       </c>
     </row>
     <row r="426" spans="1:5">
@@ -7599,10 +7599,10 @@
         <v>17864</v>
       </c>
       <c r="D426">
-        <v>36187</v>
+        <v>36191</v>
       </c>
       <c r="E426">
-        <v>58231</v>
+        <v>58280</v>
       </c>
     </row>
     <row r="427" spans="1:5">
@@ -7616,10 +7616,10 @@
         <v>17864</v>
       </c>
       <c r="D427">
-        <v>36187</v>
+        <v>36191</v>
       </c>
       <c r="E427">
-        <v>58231</v>
+        <v>58280</v>
       </c>
     </row>
     <row r="428" spans="1:5">
@@ -7633,10 +7633,10 @@
         <v>17864</v>
       </c>
       <c r="D428">
-        <v>36187</v>
+        <v>36191</v>
       </c>
       <c r="E428">
-        <v>58231</v>
+        <v>58280</v>
       </c>
     </row>
     <row r="429" spans="1:5">
@@ -7650,10 +7650,10 @@
         <v>17864</v>
       </c>
       <c r="D429">
-        <v>36187</v>
+        <v>36191</v>
       </c>
       <c r="E429">
-        <v>58231</v>
+        <v>58280</v>
       </c>
     </row>
     <row r="430" spans="1:5">
@@ -7667,10 +7667,10 @@
         <v>17864</v>
       </c>
       <c r="D430">
-        <v>36187</v>
+        <v>36191</v>
       </c>
       <c r="E430">
-        <v>58231</v>
+        <v>58280</v>
       </c>
     </row>
     <row r="431" spans="1:5">
@@ -7684,10 +7684,10 @@
         <v>17431</v>
       </c>
       <c r="D431">
-        <v>35156</v>
+        <v>35161</v>
       </c>
       <c r="E431">
-        <v>56563</v>
+        <v>56614</v>
       </c>
     </row>
     <row r="432" spans="1:5">
@@ -7701,10 +7701,10 @@
         <v>17864</v>
       </c>
       <c r="D432">
-        <v>36187</v>
+        <v>36191</v>
       </c>
       <c r="E432">
-        <v>58231</v>
+        <v>58280</v>
       </c>
     </row>
     <row r="433" spans="1:5">
@@ -7718,10 +7718,10 @@
         <v>17864</v>
       </c>
       <c r="D433">
-        <v>36187</v>
+        <v>36191</v>
       </c>
       <c r="E433">
-        <v>58231</v>
+        <v>58280</v>
       </c>
     </row>
     <row r="434" spans="1:5">
@@ -7735,10 +7735,10 @@
         <v>13377</v>
       </c>
       <c r="D434">
-        <v>29092</v>
+        <v>29093</v>
       </c>
       <c r="E434">
-        <v>48126</v>
+        <v>48145</v>
       </c>
     </row>
     <row r="435" spans="1:5">
@@ -7752,10 +7752,10 @@
         <v>17864</v>
       </c>
       <c r="D435">
-        <v>36187</v>
+        <v>36191</v>
       </c>
       <c r="E435">
-        <v>58231</v>
+        <v>58280</v>
       </c>
     </row>
     <row r="436" spans="1:5">
@@ -7769,10 +7769,10 @@
         <v>11667</v>
       </c>
       <c r="D436">
-        <v>28306</v>
+        <v>28320</v>
       </c>
       <c r="E436">
-        <v>47933</v>
+        <v>48024</v>
       </c>
     </row>
     <row r="437" spans="1:5">
@@ -7786,10 +7786,10 @@
         <v>9791</v>
       </c>
       <c r="D437">
-        <v>23684</v>
+        <v>23685</v>
       </c>
       <c r="E437">
-        <v>39860</v>
+        <v>39868</v>
       </c>
     </row>
     <row r="438" spans="1:5">
@@ -7803,10 +7803,10 @@
         <v>9791</v>
       </c>
       <c r="D438">
-        <v>23684</v>
+        <v>23685</v>
       </c>
       <c r="E438">
-        <v>39860</v>
+        <v>39868</v>
       </c>
     </row>
     <row r="439" spans="1:5">
@@ -7820,10 +7820,10 @@
         <v>9791</v>
       </c>
       <c r="D439">
-        <v>23684</v>
+        <v>23685</v>
       </c>
       <c r="E439">
-        <v>39860</v>
+        <v>39868</v>
       </c>
     </row>
     <row r="440" spans="1:5">
@@ -7837,10 +7837,10 @@
         <v>9791</v>
       </c>
       <c r="D440">
-        <v>23684</v>
+        <v>23685</v>
       </c>
       <c r="E440">
-        <v>39860</v>
+        <v>39868</v>
       </c>
     </row>
     <row r="441" spans="1:5">
@@ -7854,10 +7854,10 @@
         <v>9791</v>
       </c>
       <c r="D441">
-        <v>23684</v>
+        <v>23685</v>
       </c>
       <c r="E441">
-        <v>39860</v>
+        <v>39868</v>
       </c>
     </row>
     <row r="442" spans="1:5">
@@ -7871,10 +7871,10 @@
         <v>9791</v>
       </c>
       <c r="D442">
-        <v>23684</v>
+        <v>23685</v>
       </c>
       <c r="E442">
-        <v>39860</v>
+        <v>39868</v>
       </c>
     </row>
     <row r="443" spans="1:5">
@@ -7888,10 +7888,10 @@
         <v>9791</v>
       </c>
       <c r="D443">
-        <v>23684</v>
+        <v>23685</v>
       </c>
       <c r="E443">
-        <v>39860</v>
+        <v>39868</v>
       </c>
     </row>
     <row r="444" spans="1:5">
@@ -7905,10 +7905,10 @@
         <v>9791</v>
       </c>
       <c r="D444">
-        <v>23684</v>
+        <v>23685</v>
       </c>
       <c r="E444">
-        <v>39860</v>
+        <v>39868</v>
       </c>
     </row>
     <row r="445" spans="1:5">
@@ -7922,10 +7922,10 @@
         <v>9791</v>
       </c>
       <c r="D445">
-        <v>23684</v>
+        <v>23685</v>
       </c>
       <c r="E445">
-        <v>39860</v>
+        <v>39868</v>
       </c>
     </row>
     <row r="446" spans="1:5">
@@ -7939,10 +7939,10 @@
         <v>9791</v>
       </c>
       <c r="D446">
-        <v>23684</v>
+        <v>23685</v>
       </c>
       <c r="E446">
-        <v>39860</v>
+        <v>39868</v>
       </c>
     </row>
     <row r="447" spans="1:5">
@@ -7956,10 +7956,10 @@
         <v>9791</v>
       </c>
       <c r="D447">
-        <v>23684</v>
+        <v>23685</v>
       </c>
       <c r="E447">
-        <v>39860</v>
+        <v>39868</v>
       </c>
     </row>
     <row r="448" spans="1:5">
@@ -7973,10 +7973,10 @@
         <v>25790</v>
       </c>
       <c r="D448">
-        <v>43564</v>
+        <v>43571</v>
       </c>
       <c r="E448">
-        <v>65464</v>
+        <v>65505</v>
       </c>
     </row>
     <row r="449" spans="1:5">
@@ -7990,10 +7990,10 @@
         <v>25790</v>
       </c>
       <c r="D449">
-        <v>43564</v>
+        <v>43571</v>
       </c>
       <c r="E449">
-        <v>65464</v>
+        <v>65505</v>
       </c>
     </row>
     <row r="450" spans="1:5">
@@ -8007,10 +8007,10 @@
         <v>25790</v>
       </c>
       <c r="D450">
-        <v>43564</v>
+        <v>43571</v>
       </c>
       <c r="E450">
-        <v>65464</v>
+        <v>65505</v>
       </c>
     </row>
     <row r="451" spans="1:5">
@@ -8024,10 +8024,10 @@
         <v>25790</v>
       </c>
       <c r="D451">
-        <v>43564</v>
+        <v>43571</v>
       </c>
       <c r="E451">
-        <v>65464</v>
+        <v>65505</v>
       </c>
     </row>
     <row r="452" spans="1:5">
@@ -8041,10 +8041,10 @@
         <v>25790</v>
       </c>
       <c r="D452">
-        <v>43564</v>
+        <v>43571</v>
       </c>
       <c r="E452">
-        <v>65464</v>
+        <v>65505</v>
       </c>
     </row>
     <row r="453" spans="1:5">
@@ -8058,10 +8058,10 @@
         <v>25790</v>
       </c>
       <c r="D453">
-        <v>43564</v>
+        <v>43571</v>
       </c>
       <c r="E453">
-        <v>65464</v>
+        <v>65505</v>
       </c>
     </row>
     <row r="454" spans="1:5">
@@ -8072,13 +8072,13 @@
         <v>16246</v>
       </c>
       <c r="C454">
-        <v>21594</v>
+        <v>21598</v>
       </c>
       <c r="D454">
-        <v>40220</v>
+        <v>40223</v>
       </c>
       <c r="E454">
-        <v>62476</v>
+        <v>62496</v>
       </c>
     </row>
     <row r="455" spans="1:5">
@@ -8089,13 +8089,13 @@
         <v>16246</v>
       </c>
       <c r="C455">
-        <v>21594</v>
+        <v>21598</v>
       </c>
       <c r="D455">
-        <v>40220</v>
+        <v>40223</v>
       </c>
       <c r="E455">
-        <v>62476</v>
+        <v>62496</v>
       </c>
     </row>
     <row r="456" spans="1:5">
@@ -8106,13 +8106,13 @@
         <v>16246</v>
       </c>
       <c r="C456">
-        <v>21594</v>
+        <v>21598</v>
       </c>
       <c r="D456">
-        <v>40220</v>
+        <v>40223</v>
       </c>
       <c r="E456">
-        <v>62476</v>
+        <v>62496</v>
       </c>
     </row>
     <row r="457" spans="1:5">
@@ -8123,13 +8123,13 @@
         <v>16246</v>
       </c>
       <c r="C457">
-        <v>21594</v>
+        <v>21598</v>
       </c>
       <c r="D457">
-        <v>40220</v>
+        <v>40223</v>
       </c>
       <c r="E457">
-        <v>62476</v>
+        <v>62496</v>
       </c>
     </row>
     <row r="458" spans="1:5">
@@ -8140,13 +8140,13 @@
         <v>16246</v>
       </c>
       <c r="C458">
-        <v>21594</v>
+        <v>21598</v>
       </c>
       <c r="D458">
-        <v>40220</v>
+        <v>40223</v>
       </c>
       <c r="E458">
-        <v>62476</v>
+        <v>62496</v>
       </c>
     </row>
     <row r="459" spans="1:5">
@@ -8157,13 +8157,13 @@
         <v>16246</v>
       </c>
       <c r="C459">
-        <v>21594</v>
+        <v>21598</v>
       </c>
       <c r="D459">
-        <v>40220</v>
+        <v>40223</v>
       </c>
       <c r="E459">
-        <v>62476</v>
+        <v>62496</v>
       </c>
     </row>
     <row r="460" spans="1:5">
@@ -8174,13 +8174,13 @@
         <v>16246</v>
       </c>
       <c r="C460">
-        <v>21594</v>
+        <v>21598</v>
       </c>
       <c r="D460">
-        <v>40220</v>
+        <v>40223</v>
       </c>
       <c r="E460">
-        <v>62476</v>
+        <v>62496</v>
       </c>
     </row>
     <row r="461" spans="1:5">
@@ -8191,13 +8191,13 @@
         <v>16246</v>
       </c>
       <c r="C461">
-        <v>21594</v>
+        <v>21598</v>
       </c>
       <c r="D461">
-        <v>40220</v>
+        <v>40223</v>
       </c>
       <c r="E461">
-        <v>62476</v>
+        <v>62496</v>
       </c>
     </row>
     <row r="462" spans="1:5">
@@ -8208,13 +8208,13 @@
         <v>16246</v>
       </c>
       <c r="C462">
-        <v>21594</v>
+        <v>21598</v>
       </c>
       <c r="D462">
-        <v>40220</v>
+        <v>40223</v>
       </c>
       <c r="E462">
-        <v>62476</v>
+        <v>62496</v>
       </c>
     </row>
     <row r="463" spans="1:5">
@@ -8228,10 +8228,10 @@
         <v>17864</v>
       </c>
       <c r="D463">
-        <v>36187</v>
+        <v>36191</v>
       </c>
       <c r="E463">
-        <v>58231</v>
+        <v>58280</v>
       </c>
     </row>
     <row r="464" spans="1:5">
@@ -8245,10 +8245,10 @@
         <v>17864</v>
       </c>
       <c r="D464">
-        <v>36187</v>
+        <v>36191</v>
       </c>
       <c r="E464">
-        <v>58231</v>
+        <v>58280</v>
       </c>
     </row>
     <row r="465" spans="1:5">
@@ -8262,10 +8262,10 @@
         <v>13377</v>
       </c>
       <c r="D465">
-        <v>29092</v>
+        <v>29093</v>
       </c>
       <c r="E465">
-        <v>48126</v>
+        <v>48145</v>
       </c>
     </row>
     <row r="466" spans="1:5">
@@ -8279,10 +8279,10 @@
         <v>13377</v>
       </c>
       <c r="D466">
-        <v>29092</v>
+        <v>29093</v>
       </c>
       <c r="E466">
-        <v>48126</v>
+        <v>48145</v>
       </c>
     </row>
     <row r="467" spans="1:5">
@@ -8296,10 +8296,10 @@
         <v>17864</v>
       </c>
       <c r="D467">
-        <v>36187</v>
+        <v>36191</v>
       </c>
       <c r="E467">
-        <v>58231</v>
+        <v>58280</v>
       </c>
     </row>
     <row r="468" spans="1:5">
@@ -8313,10 +8313,10 @@
         <v>25790</v>
       </c>
       <c r="D468">
-        <v>43564</v>
+        <v>43571</v>
       </c>
       <c r="E468">
-        <v>65464</v>
+        <v>65505</v>
       </c>
     </row>
     <row r="469" spans="1:5">
@@ -8330,10 +8330,10 @@
         <v>25790</v>
       </c>
       <c r="D469">
-        <v>43564</v>
+        <v>43571</v>
       </c>
       <c r="E469">
-        <v>65464</v>
+        <v>65505</v>
       </c>
     </row>
     <row r="470" spans="1:5">
@@ -8347,10 +8347,10 @@
         <v>25790</v>
       </c>
       <c r="D470">
-        <v>43564</v>
+        <v>43571</v>
       </c>
       <c r="E470">
-        <v>65464</v>
+        <v>65505</v>
       </c>
     </row>
     <row r="471" spans="1:5">
@@ -8364,10 +8364,10 @@
         <v>17864</v>
       </c>
       <c r="D471">
-        <v>36187</v>
+        <v>36191</v>
       </c>
       <c r="E471">
-        <v>58231</v>
+        <v>58280</v>
       </c>
     </row>
     <row r="472" spans="1:5">
@@ -8378,13 +8378,13 @@
         <v>16246</v>
       </c>
       <c r="C472">
-        <v>21594</v>
+        <v>21598</v>
       </c>
       <c r="D472">
-        <v>40220</v>
+        <v>40223</v>
       </c>
       <c r="E472">
-        <v>62476</v>
+        <v>62496</v>
       </c>
     </row>
     <row r="473" spans="1:5">
@@ -8398,10 +8398,10 @@
         <v>13377</v>
       </c>
       <c r="D473">
-        <v>29092</v>
+        <v>29093</v>
       </c>
       <c r="E473">
-        <v>48126</v>
+        <v>48145</v>
       </c>
     </row>
     <row r="474" spans="1:5">
@@ -8415,10 +8415,10 @@
         <v>13377</v>
       </c>
       <c r="D474">
-        <v>29092</v>
+        <v>29093</v>
       </c>
       <c r="E474">
-        <v>48126</v>
+        <v>48145</v>
       </c>
     </row>
     <row r="475" spans="1:5">
@@ -8432,10 +8432,10 @@
         <v>11667</v>
       </c>
       <c r="D475">
-        <v>28306</v>
+        <v>28320</v>
       </c>
       <c r="E475">
-        <v>47933</v>
+        <v>48024</v>
       </c>
     </row>
     <row r="476" spans="1:5">
@@ -8449,10 +8449,10 @@
         <v>12132</v>
       </c>
       <c r="D476">
-        <v>28255</v>
+        <v>28258</v>
       </c>
       <c r="E476">
-        <v>47293</v>
+        <v>47315</v>
       </c>
     </row>
     <row r="477" spans="1:5">
@@ -8466,10 +8466,10 @@
         <v>12132</v>
       </c>
       <c r="D477">
-        <v>28255</v>
+        <v>28258</v>
       </c>
       <c r="E477">
-        <v>47293</v>
+        <v>47315</v>
       </c>
     </row>
     <row r="478" spans="1:5">
@@ -8483,10 +8483,10 @@
         <v>14077</v>
       </c>
       <c r="D478">
-        <v>31675</v>
+        <v>31679</v>
       </c>
       <c r="E478">
-        <v>53131</v>
+        <v>53171</v>
       </c>
     </row>
     <row r="479" spans="1:5">
@@ -8500,10 +8500,10 @@
         <v>12808</v>
       </c>
       <c r="D479">
-        <v>29792</v>
+        <v>29793</v>
       </c>
       <c r="E479">
-        <v>50613</v>
+        <v>50629</v>
       </c>
     </row>
     <row r="480" spans="1:5">
@@ -8517,10 +8517,10 @@
         <v>14445</v>
       </c>
       <c r="D480">
-        <v>32674</v>
+        <v>32678</v>
       </c>
       <c r="E480">
-        <v>54819</v>
+        <v>54858</v>
       </c>
     </row>
     <row r="481" spans="1:5">
@@ -8534,10 +8534,10 @@
         <v>14077</v>
       </c>
       <c r="D481">
-        <v>31675</v>
+        <v>31679</v>
       </c>
       <c r="E481">
-        <v>53131</v>
+        <v>53171</v>
       </c>
     </row>
     <row r="482" spans="1:5">
@@ -8551,10 +8551,10 @@
         <v>14077</v>
       </c>
       <c r="D482">
-        <v>31675</v>
+        <v>31679</v>
       </c>
       <c r="E482">
-        <v>53131</v>
+        <v>53171</v>
       </c>
     </row>
     <row r="483" spans="1:5">
@@ -8568,10 +8568,10 @@
         <v>14077</v>
       </c>
       <c r="D483">
-        <v>31675</v>
+        <v>31679</v>
       </c>
       <c r="E483">
-        <v>53131</v>
+        <v>53171</v>
       </c>
     </row>
     <row r="484" spans="1:5">
@@ -8585,10 +8585,10 @@
         <v>14077</v>
       </c>
       <c r="D484">
-        <v>31675</v>
+        <v>31679</v>
       </c>
       <c r="E484">
-        <v>53131</v>
+        <v>53171</v>
       </c>
     </row>
     <row r="485" spans="1:5">
@@ -8602,10 +8602,10 @@
         <v>14445</v>
       </c>
       <c r="D485">
-        <v>32674</v>
+        <v>32678</v>
       </c>
       <c r="E485">
-        <v>54819</v>
+        <v>54858</v>
       </c>
     </row>
     <row r="486" spans="1:5">
@@ -8619,10 +8619,10 @@
         <v>14064</v>
       </c>
       <c r="D486">
-        <v>32002</v>
+        <v>32003</v>
       </c>
       <c r="E486">
-        <v>53860</v>
+        <v>53881</v>
       </c>
     </row>
     <row r="487" spans="1:5">
@@ -8636,10 +8636,10 @@
         <v>12913</v>
       </c>
       <c r="D487">
-        <v>29264</v>
+        <v>29265</v>
       </c>
       <c r="E487">
-        <v>49280</v>
+        <v>49301</v>
       </c>
     </row>
     <row r="488" spans="1:5">
@@ -8650,13 +8650,13 @@
         <v>8734</v>
       </c>
       <c r="C488">
-        <v>12989</v>
+        <v>12990</v>
       </c>
       <c r="D488">
-        <v>29596</v>
+        <v>29608</v>
       </c>
       <c r="E488">
-        <v>49792</v>
+        <v>49862</v>
       </c>
     </row>
     <row r="489" spans="1:5">
@@ -8667,13 +8667,13 @@
         <v>8734</v>
       </c>
       <c r="C489">
-        <v>12989</v>
+        <v>12990</v>
       </c>
       <c r="D489">
-        <v>29596</v>
+        <v>29608</v>
       </c>
       <c r="E489">
-        <v>49792</v>
+        <v>49862</v>
       </c>
     </row>
     <row r="490" spans="1:5">
@@ -8687,10 +8687,10 @@
         <v>20019</v>
       </c>
       <c r="D490">
-        <v>41356</v>
+        <v>41367</v>
       </c>
       <c r="E490">
-        <v>65898</v>
+        <v>65970</v>
       </c>
     </row>
     <row r="491" spans="1:5">
@@ -8704,10 +8704,10 @@
         <v>20019</v>
       </c>
       <c r="D491">
-        <v>41356</v>
+        <v>41367</v>
       </c>
       <c r="E491">
-        <v>65898</v>
+        <v>65970</v>
       </c>
     </row>
     <row r="492" spans="1:5">
@@ -8721,10 +8721,10 @@
         <v>20019</v>
       </c>
       <c r="D492">
-        <v>41356</v>
+        <v>41367</v>
       </c>
       <c r="E492">
-        <v>65898</v>
+        <v>65970</v>
       </c>
     </row>
     <row r="493" spans="1:5">
@@ -8738,10 +8738,10 @@
         <v>20019</v>
       </c>
       <c r="D493">
-        <v>41356</v>
+        <v>41367</v>
       </c>
       <c r="E493">
-        <v>65898</v>
+        <v>65970</v>
       </c>
     </row>
     <row r="494" spans="1:5">
@@ -8755,10 +8755,10 @@
         <v>20019</v>
       </c>
       <c r="D494">
-        <v>41356</v>
+        <v>41367</v>
       </c>
       <c r="E494">
-        <v>65898</v>
+        <v>65970</v>
       </c>
     </row>
     <row r="495" spans="1:5">
@@ -8769,13 +8769,13 @@
         <v>10602</v>
       </c>
       <c r="C495">
-        <v>18154</v>
+        <v>18165</v>
       </c>
       <c r="D495">
-        <v>41036</v>
+        <v>41200</v>
       </c>
       <c r="E495">
-        <v>66607</v>
+        <v>67046</v>
       </c>
     </row>
     <row r="496" spans="1:5">
@@ -8786,13 +8786,13 @@
         <v>13211</v>
       </c>
       <c r="C496">
-        <v>21080</v>
+        <v>21081</v>
       </c>
       <c r="D496">
-        <v>44075</v>
+        <v>44145</v>
       </c>
       <c r="E496">
-        <v>69476</v>
+        <v>69773</v>
       </c>
     </row>
     <row r="497" spans="1:5">
@@ -8803,13 +8803,13 @@
         <v>10602</v>
       </c>
       <c r="C497">
-        <v>18154</v>
+        <v>18165</v>
       </c>
       <c r="D497">
-        <v>41036</v>
+        <v>41200</v>
       </c>
       <c r="E497">
-        <v>66607</v>
+        <v>67046</v>
       </c>
     </row>
     <row r="498" spans="1:5">
@@ -8820,13 +8820,13 @@
         <v>14143</v>
       </c>
       <c r="C498">
-        <v>20407</v>
+        <v>20408</v>
       </c>
       <c r="D498">
-        <v>40106</v>
+        <v>40222</v>
       </c>
       <c r="E498">
-        <v>62979</v>
+        <v>63345</v>
       </c>
     </row>
     <row r="499" spans="1:5">
@@ -8837,13 +8837,13 @@
         <v>14143</v>
       </c>
       <c r="C499">
-        <v>20407</v>
+        <v>20408</v>
       </c>
       <c r="D499">
-        <v>40106</v>
+        <v>40222</v>
       </c>
       <c r="E499">
-        <v>62979</v>
+        <v>63345</v>
       </c>
     </row>
     <row r="500" spans="1:5">
@@ -8854,13 +8854,13 @@
         <v>14143</v>
       </c>
       <c r="C500">
-        <v>20407</v>
+        <v>20408</v>
       </c>
       <c r="D500">
-        <v>40106</v>
+        <v>40222</v>
       </c>
       <c r="E500">
-        <v>62979</v>
+        <v>63345</v>
       </c>
     </row>
     <row r="501" spans="1:5">
@@ -8874,10 +8874,10 @@
         <v>14829</v>
       </c>
       <c r="D501">
-        <v>31365</v>
+        <v>31374</v>
       </c>
       <c r="E501">
-        <v>51691</v>
+        <v>51766</v>
       </c>
     </row>
   </sheetData>
